--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_18-07-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_18-07-2025.xlsx
@@ -538,17 +538,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>£11.15</t>
+          <t>£10.98</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>£11.15</t>
+          <t>£10.98</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>£11.15</t>
+          <t>£10.98</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -591,25 +591,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c57e925+77845]
-	GetHandleVerifier [0x0x7ff61c57e980+77936]
-	(No symbol) [0x0x7ff61c339cda]
-	(No symbol) [0x0x7ff61c3906aa]
-	(No symbol) [0x0x7ff61c39095c]
-	(No symbol) [0x0x7ff61c3e3d07]
-	(No symbol) [0x0x7ff61c3b890f]
-	(No symbol) [0x0x7ff61c3e0b07]
-	(No symbol) [0x0x7ff61c3b86a3]
-	(No symbol) [0x0x7ff61c381791]
-	(No symbol) [0x0x7ff61c382523]
-	GetHandleVerifier [0x0x7ff61c85683d+3059501]
-	GetHandleVerifier [0x0x7ff61c850bfd+3035885]
-	GetHandleVerifier [0x0x7ff61c8703f0+3164896]
-	GetHandleVerifier [0x0x7ff61c598c2e+185118]
-	GetHandleVerifier [0x0x7ff61c5a053f+216111]
-	GetHandleVerifier [0x0x7ff61c5872d4+113092]
-	GetHandleVerifier [0x0x7ff61c587489+113529]
-	GetHandleVerifier [0x0x7ff61c56e288+10616]
+	GetHandleVerifier [0x0x7ff62824e925+77845]
+	GetHandleVerifier [0x0x7ff62824e980+77936]
+	(No symbol) [0x0x7ff628009cda]
+	(No symbol) [0x0x7ff6280606aa]
+	(No symbol) [0x0x7ff62806095c]
+	(No symbol) [0x0x7ff6280b3d07]
+	(No symbol) [0x0x7ff62808890f]
+	(No symbol) [0x0x7ff6280b0b07]
+	(No symbol) [0x0x7ff6280886a3]
+	(No symbol) [0x0x7ff628051791]
+	(No symbol) [0x0x7ff628052523]
+	GetHandleVerifier [0x0x7ff62852683d+3059501]
+	GetHandleVerifier [0x0x7ff628520bfd+3035885]
+	GetHandleVerifier [0x0x7ff6285403f0+3164896]
+	GetHandleVerifier [0x0x7ff628268c2e+185118]
+	GetHandleVerifier [0x0x7ff62827053f+216111]
+	GetHandleVerifier [0x0x7ff6282572d4+113092]
+	GetHandleVerifier [0x0x7ff628257489+113529]
+	GetHandleVerifier [0x0x7ff62823e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -659,17 +659,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>£12.80</t>
+          <t>£12.62</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>£12.80</t>
+          <t>£12.62</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>£12.80</t>
+          <t>£12.62</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -712,25 +712,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c57e925+77845]
-	GetHandleVerifier [0x0x7ff61c57e980+77936]
-	(No symbol) [0x0x7ff61c339cda]
-	(No symbol) [0x0x7ff61c3906aa]
-	(No symbol) [0x0x7ff61c39095c]
-	(No symbol) [0x0x7ff61c3e3d07]
-	(No symbol) [0x0x7ff61c3b890f]
-	(No symbol) [0x0x7ff61c3e0b07]
-	(No symbol) [0x0x7ff61c3b86a3]
-	(No symbol) [0x0x7ff61c381791]
-	(No symbol) [0x0x7ff61c382523]
-	GetHandleVerifier [0x0x7ff61c85683d+3059501]
-	GetHandleVerifier [0x0x7ff61c850bfd+3035885]
-	GetHandleVerifier [0x0x7ff61c8703f0+3164896]
-	GetHandleVerifier [0x0x7ff61c598c2e+185118]
-	GetHandleVerifier [0x0x7ff61c5a053f+216111]
-	GetHandleVerifier [0x0x7ff61c5872d4+113092]
-	GetHandleVerifier [0x0x7ff61c587489+113529]
-	GetHandleVerifier [0x0x7ff61c56e288+10616]
+	GetHandleVerifier [0x0x7ff62824e925+77845]
+	GetHandleVerifier [0x0x7ff62824e980+77936]
+	(No symbol) [0x0x7ff628009cda]
+	(No symbol) [0x0x7ff6280606aa]
+	(No symbol) [0x0x7ff62806095c]
+	(No symbol) [0x0x7ff6280b3d07]
+	(No symbol) [0x0x7ff62808890f]
+	(No symbol) [0x0x7ff6280b0b07]
+	(No symbol) [0x0x7ff6280886a3]
+	(No symbol) [0x0x7ff628051791]
+	(No symbol) [0x0x7ff628052523]
+	GetHandleVerifier [0x0x7ff62852683d+3059501]
+	GetHandleVerifier [0x0x7ff628520bfd+3035885]
+	GetHandleVerifier [0x0x7ff6285403f0+3164896]
+	GetHandleVerifier [0x0x7ff628268c2e+185118]
+	GetHandleVerifier [0x0x7ff62827053f+216111]
+	GetHandleVerifier [0x0x7ff6282572d4+113092]
+	GetHandleVerifier [0x0x7ff628257489+113529]
+	GetHandleVerifier [0x0x7ff62823e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -780,17 +780,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>£16.46</t>
+          <t>£16.18</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>£16.46</t>
+          <t>£16.18</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>£14.46</t>
+          <t>£16.18</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -833,25 +833,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c57e925+77845]
-	GetHandleVerifier [0x0x7ff61c57e980+77936]
-	(No symbol) [0x0x7ff61c339cda]
-	(No symbol) [0x0x7ff61c3906aa]
-	(No symbol) [0x0x7ff61c39095c]
-	(No symbol) [0x0x7ff61c3e3d07]
-	(No symbol) [0x0x7ff61c3b890f]
-	(No symbol) [0x0x7ff61c3e0b07]
-	(No symbol) [0x0x7ff61c3b86a3]
-	(No symbol) [0x0x7ff61c381791]
-	(No symbol) [0x0x7ff61c382523]
-	GetHandleVerifier [0x0x7ff61c85683d+3059501]
-	GetHandleVerifier [0x0x7ff61c850bfd+3035885]
-	GetHandleVerifier [0x0x7ff61c8703f0+3164896]
-	GetHandleVerifier [0x0x7ff61c598c2e+185118]
-	GetHandleVerifier [0x0x7ff61c5a053f+216111]
-	GetHandleVerifier [0x0x7ff61c5872d4+113092]
-	GetHandleVerifier [0x0x7ff61c587489+113529]
-	GetHandleVerifier [0x0x7ff61c56e288+10616]
+	GetHandleVerifier [0x0x7ff62824e925+77845]
+	GetHandleVerifier [0x0x7ff62824e980+77936]
+	(No symbol) [0x0x7ff628009cda]
+	(No symbol) [0x0x7ff6280606aa]
+	(No symbol) [0x0x7ff62806095c]
+	(No symbol) [0x0x7ff6280b3d07]
+	(No symbol) [0x0x7ff62808890f]
+	(No symbol) [0x0x7ff6280b0b07]
+	(No symbol) [0x0x7ff6280886a3]
+	(No symbol) [0x0x7ff628051791]
+	(No symbol) [0x0x7ff628052523]
+	GetHandleVerifier [0x0x7ff62852683d+3059501]
+	GetHandleVerifier [0x0x7ff628520bfd+3035885]
+	GetHandleVerifier [0x0x7ff6285403f0+3164896]
+	GetHandleVerifier [0x0x7ff628268c2e+185118]
+	GetHandleVerifier [0x0x7ff62827053f+216111]
+	GetHandleVerifier [0x0x7ff6282572d4+113092]
+	GetHandleVerifier [0x0x7ff628257489+113529]
+	GetHandleVerifier [0x0x7ff62823e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -954,25 +954,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c57e925+77845]
-	GetHandleVerifier [0x0x7ff61c57e980+77936]
-	(No symbol) [0x0x7ff61c339cda]
-	(No symbol) [0x0x7ff61c3906aa]
-	(No symbol) [0x0x7ff61c39095c]
-	(No symbol) [0x0x7ff61c3e3d07]
-	(No symbol) [0x0x7ff61c3b890f]
-	(No symbol) [0x0x7ff61c3e0b07]
-	(No symbol) [0x0x7ff61c3b86a3]
-	(No symbol) [0x0x7ff61c381791]
-	(No symbol) [0x0x7ff61c382523]
-	GetHandleVerifier [0x0x7ff61c85683d+3059501]
-	GetHandleVerifier [0x0x7ff61c850bfd+3035885]
-	GetHandleVerifier [0x0x7ff61c8703f0+3164896]
-	GetHandleVerifier [0x0x7ff61c598c2e+185118]
-	GetHandleVerifier [0x0x7ff61c5a053f+216111]
-	GetHandleVerifier [0x0x7ff61c5872d4+113092]
-	GetHandleVerifier [0x0x7ff61c587489+113529]
-	GetHandleVerifier [0x0x7ff61c56e288+10616]
+	GetHandleVerifier [0x0x7ff62824e925+77845]
+	GetHandleVerifier [0x0x7ff62824e980+77936]
+	(No symbol) [0x0x7ff628009cda]
+	(No symbol) [0x0x7ff6280606aa]
+	(No symbol) [0x0x7ff62806095c]
+	(No symbol) [0x0x7ff6280b3d07]
+	(No symbol) [0x0x7ff62808890f]
+	(No symbol) [0x0x7ff6280b0b07]
+	(No symbol) [0x0x7ff6280886a3]
+	(No symbol) [0x0x7ff628051791]
+	(No symbol) [0x0x7ff628052523]
+	GetHandleVerifier [0x0x7ff62852683d+3059501]
+	GetHandleVerifier [0x0x7ff628520bfd+3035885]
+	GetHandleVerifier [0x0x7ff6285403f0+3164896]
+	GetHandleVerifier [0x0x7ff628268c2e+185118]
+	GetHandleVerifier [0x0x7ff62827053f+216111]
+	GetHandleVerifier [0x0x7ff6282572d4+113092]
+	GetHandleVerifier [0x0x7ff628257489+113529]
+	GetHandleVerifier [0x0x7ff62823e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -1022,17 +1022,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>£21.20</t>
+          <t>£21.08</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>£21.20</t>
+          <t>£21.08</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>£21.20</t>
+          <t>£21.08</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1075,25 +1075,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c57e925+77845]
-	GetHandleVerifier [0x0x7ff61c57e980+77936]
-	(No symbol) [0x0x7ff61c339cda]
-	(No symbol) [0x0x7ff61c3906aa]
-	(No symbol) [0x0x7ff61c39095c]
-	(No symbol) [0x0x7ff61c3e3d07]
-	(No symbol) [0x0x7ff61c3b890f]
-	(No symbol) [0x0x7ff61c3e0b07]
-	(No symbol) [0x0x7ff61c3b86a3]
-	(No symbol) [0x0x7ff61c381791]
-	(No symbol) [0x0x7ff61c382523]
-	GetHandleVerifier [0x0x7ff61c85683d+3059501]
-	GetHandleVerifier [0x0x7ff61c850bfd+3035885]
-	GetHandleVerifier [0x0x7ff61c8703f0+3164896]
-	GetHandleVerifier [0x0x7ff61c598c2e+185118]
-	GetHandleVerifier [0x0x7ff61c5a053f+216111]
-	GetHandleVerifier [0x0x7ff61c5872d4+113092]
-	GetHandleVerifier [0x0x7ff61c587489+113529]
-	GetHandleVerifier [0x0x7ff61c56e288+10616]
+	GetHandleVerifier [0x0x7ff62824e925+77845]
+	GetHandleVerifier [0x0x7ff62824e980+77936]
+	(No symbol) [0x0x7ff628009cda]
+	(No symbol) [0x0x7ff6280606aa]
+	(No symbol) [0x0x7ff62806095c]
+	(No symbol) [0x0x7ff6280b3d07]
+	(No symbol) [0x0x7ff62808890f]
+	(No symbol) [0x0x7ff6280b0b07]
+	(No symbol) [0x0x7ff6280886a3]
+	(No symbol) [0x0x7ff628051791]
+	(No symbol) [0x0x7ff628052523]
+	GetHandleVerifier [0x0x7ff62852683d+3059501]
+	GetHandleVerifier [0x0x7ff628520bfd+3035885]
+	GetHandleVerifier [0x0x7ff6285403f0+3164896]
+	GetHandleVerifier [0x0x7ff628268c2e+185118]
+	GetHandleVerifier [0x0x7ff62827053f+216111]
+	GetHandleVerifier [0x0x7ff6282572d4+113092]
+	GetHandleVerifier [0x0x7ff628257489+113529]
+	GetHandleVerifier [0x0x7ff62823e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -1143,17 +1143,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>£23.13</t>
+          <t>£22.76</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>£23.13</t>
+          <t>£22.76</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>£23.13</t>
+          <t>£22.76</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1196,25 +1196,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c57e925+77845]
-	GetHandleVerifier [0x0x7ff61c57e980+77936]
-	(No symbol) [0x0x7ff61c339cda]
-	(No symbol) [0x0x7ff61c3906aa]
-	(No symbol) [0x0x7ff61c39095c]
-	(No symbol) [0x0x7ff61c3e3d07]
-	(No symbol) [0x0x7ff61c3b890f]
-	(No symbol) [0x0x7ff61c3e0b07]
-	(No symbol) [0x0x7ff61c3b86a3]
-	(No symbol) [0x0x7ff61c381791]
-	(No symbol) [0x0x7ff61c382523]
-	GetHandleVerifier [0x0x7ff61c85683d+3059501]
-	GetHandleVerifier [0x0x7ff61c850bfd+3035885]
-	GetHandleVerifier [0x0x7ff61c8703f0+3164896]
-	GetHandleVerifier [0x0x7ff61c598c2e+185118]
-	GetHandleVerifier [0x0x7ff61c5a053f+216111]
-	GetHandleVerifier [0x0x7ff61c5872d4+113092]
-	GetHandleVerifier [0x0x7ff61c587489+113529]
-	GetHandleVerifier [0x0x7ff61c56e288+10616]
+	GetHandleVerifier [0x0x7ff62824e925+77845]
+	GetHandleVerifier [0x0x7ff62824e980+77936]
+	(No symbol) [0x0x7ff628009cda]
+	(No symbol) [0x0x7ff6280606aa]
+	(No symbol) [0x0x7ff62806095c]
+	(No symbol) [0x0x7ff6280b3d07]
+	(No symbol) [0x0x7ff62808890f]
+	(No symbol) [0x0x7ff6280b0b07]
+	(No symbol) [0x0x7ff6280886a3]
+	(No symbol) [0x0x7ff628051791]
+	(No symbol) [0x0x7ff628052523]
+	GetHandleVerifier [0x0x7ff62852683d+3059501]
+	GetHandleVerifier [0x0x7ff628520bfd+3035885]
+	GetHandleVerifier [0x0x7ff6285403f0+3164896]
+	GetHandleVerifier [0x0x7ff628268c2e+185118]
+	GetHandleVerifier [0x0x7ff62827053f+216111]
+	GetHandleVerifier [0x0x7ff6282572d4+113092]
+	GetHandleVerifier [0x0x7ff628257489+113529]
+	GetHandleVerifier [0x0x7ff62823e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -1317,25 +1317,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c57e925+77845]
-	GetHandleVerifier [0x0x7ff61c57e980+77936]
-	(No symbol) [0x0x7ff61c339cda]
-	(No symbol) [0x0x7ff61c3906aa]
-	(No symbol) [0x0x7ff61c39095c]
-	(No symbol) [0x0x7ff61c3e3d07]
-	(No symbol) [0x0x7ff61c3b890f]
-	(No symbol) [0x0x7ff61c3e0b07]
-	(No symbol) [0x0x7ff61c3b86a3]
-	(No symbol) [0x0x7ff61c381791]
-	(No symbol) [0x0x7ff61c382523]
-	GetHandleVerifier [0x0x7ff61c85683d+3059501]
-	GetHandleVerifier [0x0x7ff61c850bfd+3035885]
-	GetHandleVerifier [0x0x7ff61c8703f0+3164896]
-	GetHandleVerifier [0x0x7ff61c598c2e+185118]
-	GetHandleVerifier [0x0x7ff61c5a053f+216111]
-	GetHandleVerifier [0x0x7ff61c5872d4+113092]
-	GetHandleVerifier [0x0x7ff61c587489+113529]
-	GetHandleVerifier [0x0x7ff61c56e288+10616]
+	GetHandleVerifier [0x0x7ff62824e925+77845]
+	GetHandleVerifier [0x0x7ff62824e980+77936]
+	(No symbol) [0x0x7ff628009cda]
+	(No symbol) [0x0x7ff6280606aa]
+	(No symbol) [0x0x7ff62806095c]
+	(No symbol) [0x0x7ff6280b3d07]
+	(No symbol) [0x0x7ff62808890f]
+	(No symbol) [0x0x7ff6280b0b07]
+	(No symbol) [0x0x7ff6280886a3]
+	(No symbol) [0x0x7ff628051791]
+	(No symbol) [0x0x7ff628052523]
+	GetHandleVerifier [0x0x7ff62852683d+3059501]
+	GetHandleVerifier [0x0x7ff628520bfd+3035885]
+	GetHandleVerifier [0x0x7ff6285403f0+3164896]
+	GetHandleVerifier [0x0x7ff628268c2e+185118]
+	GetHandleVerifier [0x0x7ff62827053f+216111]
+	GetHandleVerifier [0x0x7ff6282572d4+113092]
+	GetHandleVerifier [0x0x7ff628257489+113529]
+	GetHandleVerifier [0x0x7ff62823e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -1438,25 +1438,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c57e925+77845]
-	GetHandleVerifier [0x0x7ff61c57e980+77936]
-	(No symbol) [0x0x7ff61c339cda]
-	(No symbol) [0x0x7ff61c3906aa]
-	(No symbol) [0x0x7ff61c39095c]
-	(No symbol) [0x0x7ff61c3e3d07]
-	(No symbol) [0x0x7ff61c3b890f]
-	(No symbol) [0x0x7ff61c3e0b07]
-	(No symbol) [0x0x7ff61c3b86a3]
-	(No symbol) [0x0x7ff61c381791]
-	(No symbol) [0x0x7ff61c382523]
-	GetHandleVerifier [0x0x7ff61c85683d+3059501]
-	GetHandleVerifier [0x0x7ff61c850bfd+3035885]
-	GetHandleVerifier [0x0x7ff61c8703f0+3164896]
-	GetHandleVerifier [0x0x7ff61c598c2e+185118]
-	GetHandleVerifier [0x0x7ff61c5a053f+216111]
-	GetHandleVerifier [0x0x7ff61c5872d4+113092]
-	GetHandleVerifier [0x0x7ff61c587489+113529]
-	GetHandleVerifier [0x0x7ff61c56e288+10616]
+	GetHandleVerifier [0x0x7ff62824e925+77845]
+	GetHandleVerifier [0x0x7ff62824e980+77936]
+	(No symbol) [0x0x7ff628009cda]
+	(No symbol) [0x0x7ff6280606aa]
+	(No symbol) [0x0x7ff62806095c]
+	(No symbol) [0x0x7ff6280b3d07]
+	(No symbol) [0x0x7ff62808890f]
+	(No symbol) [0x0x7ff6280b0b07]
+	(No symbol) [0x0x7ff6280886a3]
+	(No symbol) [0x0x7ff628051791]
+	(No symbol) [0x0x7ff628052523]
+	GetHandleVerifier [0x0x7ff62852683d+3059501]
+	GetHandleVerifier [0x0x7ff628520bfd+3035885]
+	GetHandleVerifier [0x0x7ff6285403f0+3164896]
+	GetHandleVerifier [0x0x7ff628268c2e+185118]
+	GetHandleVerifier [0x0x7ff62827053f+216111]
+	GetHandleVerifier [0x0x7ff6282572d4+113092]
+	GetHandleVerifier [0x0x7ff628257489+113529]
+	GetHandleVerifier [0x0x7ff62823e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -1506,17 +1506,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>£29.00</t>
+          <t>£28.82</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>£29.00</t>
+          <t>£28.82</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>£29.00</t>
+          <t>£28.82</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1559,25 +1559,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c57e925+77845]
-	GetHandleVerifier [0x0x7ff61c57e980+77936]
-	(No symbol) [0x0x7ff61c339cda]
-	(No symbol) [0x0x7ff61c3906aa]
-	(No symbol) [0x0x7ff61c39095c]
-	(No symbol) [0x0x7ff61c3e3d07]
-	(No symbol) [0x0x7ff61c3b890f]
-	(No symbol) [0x0x7ff61c3e0b07]
-	(No symbol) [0x0x7ff61c3b86a3]
-	(No symbol) [0x0x7ff61c381791]
-	(No symbol) [0x0x7ff61c382523]
-	GetHandleVerifier [0x0x7ff61c85683d+3059501]
-	GetHandleVerifier [0x0x7ff61c850bfd+3035885]
-	GetHandleVerifier [0x0x7ff61c8703f0+3164896]
-	GetHandleVerifier [0x0x7ff61c598c2e+185118]
-	GetHandleVerifier [0x0x7ff61c5a053f+216111]
-	GetHandleVerifier [0x0x7ff61c5872d4+113092]
-	GetHandleVerifier [0x0x7ff61c587489+113529]
-	GetHandleVerifier [0x0x7ff61c56e288+10616]
+	GetHandleVerifier [0x0x7ff62824e925+77845]
+	GetHandleVerifier [0x0x7ff62824e980+77936]
+	(No symbol) [0x0x7ff628009cda]
+	(No symbol) [0x0x7ff6280606aa]
+	(No symbol) [0x0x7ff62806095c]
+	(No symbol) [0x0x7ff6280b3d07]
+	(No symbol) [0x0x7ff62808890f]
+	(No symbol) [0x0x7ff6280b0b07]
+	(No symbol) [0x0x7ff6280886a3]
+	(No symbol) [0x0x7ff628051791]
+	(No symbol) [0x0x7ff628052523]
+	GetHandleVerifier [0x0x7ff62852683d+3059501]
+	GetHandleVerifier [0x0x7ff628520bfd+3035885]
+	GetHandleVerifier [0x0x7ff6285403f0+3164896]
+	GetHandleVerifier [0x0x7ff628268c2e+185118]
+	GetHandleVerifier [0x0x7ff62827053f+216111]
+	GetHandleVerifier [0x0x7ff6282572d4+113092]
+	GetHandleVerifier [0x0x7ff628257489+113529]
+	GetHandleVerifier [0x0x7ff62823e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -1627,17 +1627,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>£29.00</t>
+          <t>£28.99</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>£29.00</t>
+          <t>£28.99</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>£29.00</t>
+          <t>£28.99</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1680,25 +1680,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c57e925+77845]
-	GetHandleVerifier [0x0x7ff61c57e980+77936]
-	(No symbol) [0x0x7ff61c339cda]
-	(No symbol) [0x0x7ff61c3906aa]
-	(No symbol) [0x0x7ff61c39095c]
-	(No symbol) [0x0x7ff61c3e3d07]
-	(No symbol) [0x0x7ff61c3b890f]
-	(No symbol) [0x0x7ff61c3e0b07]
-	(No symbol) [0x0x7ff61c3b86a3]
-	(No symbol) [0x0x7ff61c381791]
-	(No symbol) [0x0x7ff61c382523]
-	GetHandleVerifier [0x0x7ff61c85683d+3059501]
-	GetHandleVerifier [0x0x7ff61c850bfd+3035885]
-	GetHandleVerifier [0x0x7ff61c8703f0+3164896]
-	GetHandleVerifier [0x0x7ff61c598c2e+185118]
-	GetHandleVerifier [0x0x7ff61c5a053f+216111]
-	GetHandleVerifier [0x0x7ff61c5872d4+113092]
-	GetHandleVerifier [0x0x7ff61c587489+113529]
-	GetHandleVerifier [0x0x7ff61c56e288+10616]
+	GetHandleVerifier [0x0x7ff62824e925+77845]
+	GetHandleVerifier [0x0x7ff62824e980+77936]
+	(No symbol) [0x0x7ff628009cda]
+	(No symbol) [0x0x7ff6280606aa]
+	(No symbol) [0x0x7ff62806095c]
+	(No symbol) [0x0x7ff6280b3d07]
+	(No symbol) [0x0x7ff62808890f]
+	(No symbol) [0x0x7ff6280b0b07]
+	(No symbol) [0x0x7ff6280886a3]
+	(No symbol) [0x0x7ff628051791]
+	(No symbol) [0x0x7ff628052523]
+	GetHandleVerifier [0x0x7ff62852683d+3059501]
+	GetHandleVerifier [0x0x7ff628520bfd+3035885]
+	GetHandleVerifier [0x0x7ff6285403f0+3164896]
+	GetHandleVerifier [0x0x7ff628268c2e+185118]
+	GetHandleVerifier [0x0x7ff62827053f+216111]
+	GetHandleVerifier [0x0x7ff6282572d4+113092]
+	GetHandleVerifier [0x0x7ff628257489+113529]
+	GetHandleVerifier [0x0x7ff62823e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -1801,25 +1801,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c57e925+77845]
-	GetHandleVerifier [0x0x7ff61c57e980+77936]
-	(No symbol) [0x0x7ff61c339cda]
-	(No symbol) [0x0x7ff61c3906aa]
-	(No symbol) [0x0x7ff61c39095c]
-	(No symbol) [0x0x7ff61c3e3d07]
-	(No symbol) [0x0x7ff61c3b890f]
-	(No symbol) [0x0x7ff61c3e0b07]
-	(No symbol) [0x0x7ff61c3b86a3]
-	(No symbol) [0x0x7ff61c381791]
-	(No symbol) [0x0x7ff61c382523]
-	GetHandleVerifier [0x0x7ff61c85683d+3059501]
-	GetHandleVerifier [0x0x7ff61c850bfd+3035885]
-	GetHandleVerifier [0x0x7ff61c8703f0+3164896]
-	GetHandleVerifier [0x0x7ff61c598c2e+185118]
-	GetHandleVerifier [0x0x7ff61c5a053f+216111]
-	GetHandleVerifier [0x0x7ff61c5872d4+113092]
-	GetHandleVerifier [0x0x7ff61c587489+113529]
-	GetHandleVerifier [0x0x7ff61c56e288+10616]
+	GetHandleVerifier [0x0x7ff62824e925+77845]
+	GetHandleVerifier [0x0x7ff62824e980+77936]
+	(No symbol) [0x0x7ff628009cda]
+	(No symbol) [0x0x7ff6280606aa]
+	(No symbol) [0x0x7ff62806095c]
+	(No symbol) [0x0x7ff6280b3d07]
+	(No symbol) [0x0x7ff62808890f]
+	(No symbol) [0x0x7ff6280b0b07]
+	(No symbol) [0x0x7ff6280886a3]
+	(No symbol) [0x0x7ff628051791]
+	(No symbol) [0x0x7ff628052523]
+	GetHandleVerifier [0x0x7ff62852683d+3059501]
+	GetHandleVerifier [0x0x7ff628520bfd+3035885]
+	GetHandleVerifier [0x0x7ff6285403f0+3164896]
+	GetHandleVerifier [0x0x7ff628268c2e+185118]
+	GetHandleVerifier [0x0x7ff62827053f+216111]
+	GetHandleVerifier [0x0x7ff6282572d4+113092]
+	GetHandleVerifier [0x0x7ff628257489+113529]
+	GetHandleVerifier [0x0x7ff62823e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -1869,17 +1869,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>£35.85</t>
+          <t>£34.99</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>£35.85</t>
+          <t>£34.99</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>£35.85</t>
+          <t>£34.99</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1922,25 +1922,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c57e925+77845]
-	GetHandleVerifier [0x0x7ff61c57e980+77936]
-	(No symbol) [0x0x7ff61c339cda]
-	(No symbol) [0x0x7ff61c3906aa]
-	(No symbol) [0x0x7ff61c39095c]
-	(No symbol) [0x0x7ff61c3e3d07]
-	(No symbol) [0x0x7ff61c3b890f]
-	(No symbol) [0x0x7ff61c3e0b07]
-	(No symbol) [0x0x7ff61c3b86a3]
-	(No symbol) [0x0x7ff61c381791]
-	(No symbol) [0x0x7ff61c382523]
-	GetHandleVerifier [0x0x7ff61c85683d+3059501]
-	GetHandleVerifier [0x0x7ff61c850bfd+3035885]
-	GetHandleVerifier [0x0x7ff61c8703f0+3164896]
-	GetHandleVerifier [0x0x7ff61c598c2e+185118]
-	GetHandleVerifier [0x0x7ff61c5a053f+216111]
-	GetHandleVerifier [0x0x7ff61c5872d4+113092]
-	GetHandleVerifier [0x0x7ff61c587489+113529]
-	GetHandleVerifier [0x0x7ff61c56e288+10616]
+	GetHandleVerifier [0x0x7ff62824e925+77845]
+	GetHandleVerifier [0x0x7ff62824e980+77936]
+	(No symbol) [0x0x7ff628009cda]
+	(No symbol) [0x0x7ff6280606aa]
+	(No symbol) [0x0x7ff62806095c]
+	(No symbol) [0x0x7ff6280b3d07]
+	(No symbol) [0x0x7ff62808890f]
+	(No symbol) [0x0x7ff6280b0b07]
+	(No symbol) [0x0x7ff6280886a3]
+	(No symbol) [0x0x7ff628051791]
+	(No symbol) [0x0x7ff628052523]
+	GetHandleVerifier [0x0x7ff62852683d+3059501]
+	GetHandleVerifier [0x0x7ff628520bfd+3035885]
+	GetHandleVerifier [0x0x7ff6285403f0+3164896]
+	GetHandleVerifier [0x0x7ff628268c2e+185118]
+	GetHandleVerifier [0x0x7ff62827053f+216111]
+	GetHandleVerifier [0x0x7ff6282572d4+113092]
+	GetHandleVerifier [0x0x7ff628257489+113529]
+	GetHandleVerifier [0x0x7ff62823e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -2043,25 +2043,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c57e925+77845]
-	GetHandleVerifier [0x0x7ff61c57e980+77936]
-	(No symbol) [0x0x7ff61c339cda]
-	(No symbol) [0x0x7ff61c3906aa]
-	(No symbol) [0x0x7ff61c39095c]
-	(No symbol) [0x0x7ff61c3e3d07]
-	(No symbol) [0x0x7ff61c3b890f]
-	(No symbol) [0x0x7ff61c3e0b07]
-	(No symbol) [0x0x7ff61c3b86a3]
-	(No symbol) [0x0x7ff61c381791]
-	(No symbol) [0x0x7ff61c382523]
-	GetHandleVerifier [0x0x7ff61c85683d+3059501]
-	GetHandleVerifier [0x0x7ff61c850bfd+3035885]
-	GetHandleVerifier [0x0x7ff61c8703f0+3164896]
-	GetHandleVerifier [0x0x7ff61c598c2e+185118]
-	GetHandleVerifier [0x0x7ff61c5a053f+216111]
-	GetHandleVerifier [0x0x7ff61c5872d4+113092]
-	GetHandleVerifier [0x0x7ff61c587489+113529]
-	GetHandleVerifier [0x0x7ff61c56e288+10616]
+	GetHandleVerifier [0x0x7ff62824e925+77845]
+	GetHandleVerifier [0x0x7ff62824e980+77936]
+	(No symbol) [0x0x7ff628009cda]
+	(No symbol) [0x0x7ff6280606aa]
+	(No symbol) [0x0x7ff62806095c]
+	(No symbol) [0x0x7ff6280b3d07]
+	(No symbol) [0x0x7ff62808890f]
+	(No symbol) [0x0x7ff6280b0b07]
+	(No symbol) [0x0x7ff6280886a3]
+	(No symbol) [0x0x7ff628051791]
+	(No symbol) [0x0x7ff628052523]
+	GetHandleVerifier [0x0x7ff62852683d+3059501]
+	GetHandleVerifier [0x0x7ff628520bfd+3035885]
+	GetHandleVerifier [0x0x7ff6285403f0+3164896]
+	GetHandleVerifier [0x0x7ff628268c2e+185118]
+	GetHandleVerifier [0x0x7ff62827053f+216111]
+	GetHandleVerifier [0x0x7ff6282572d4+113092]
+	GetHandleVerifier [0x0x7ff628257489+113529]
+	GetHandleVerifier [0x0x7ff62823e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -2111,12 +2111,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>£44.50</t>
+          <t>£43.99</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>£44.50</t>
+          <t>£43.99</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2164,25 +2164,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c57e925+77845]
-	GetHandleVerifier [0x0x7ff61c57e980+77936]
-	(No symbol) [0x0x7ff61c339cda]
-	(No symbol) [0x0x7ff61c3906aa]
-	(No symbol) [0x0x7ff61c39095c]
-	(No symbol) [0x0x7ff61c3e3d07]
-	(No symbol) [0x0x7ff61c3b890f]
-	(No symbol) [0x0x7ff61c3e0b07]
-	(No symbol) [0x0x7ff61c3b86a3]
-	(No symbol) [0x0x7ff61c381791]
-	(No symbol) [0x0x7ff61c382523]
-	GetHandleVerifier [0x0x7ff61c85683d+3059501]
-	GetHandleVerifier [0x0x7ff61c850bfd+3035885]
-	GetHandleVerifier [0x0x7ff61c8703f0+3164896]
-	GetHandleVerifier [0x0x7ff61c598c2e+185118]
-	GetHandleVerifier [0x0x7ff61c5a053f+216111]
-	GetHandleVerifier [0x0x7ff61c5872d4+113092]
-	GetHandleVerifier [0x0x7ff61c587489+113529]
-	GetHandleVerifier [0x0x7ff61c56e288+10616]
+	GetHandleVerifier [0x0x7ff62824e925+77845]
+	GetHandleVerifier [0x0x7ff62824e980+77936]
+	(No symbol) [0x0x7ff628009cda]
+	(No symbol) [0x0x7ff6280606aa]
+	(No symbol) [0x0x7ff62806095c]
+	(No symbol) [0x0x7ff6280b3d07]
+	(No symbol) [0x0x7ff62808890f]
+	(No symbol) [0x0x7ff6280b0b07]
+	(No symbol) [0x0x7ff6280886a3]
+	(No symbol) [0x0x7ff628051791]
+	(No symbol) [0x0x7ff628052523]
+	GetHandleVerifier [0x0x7ff62852683d+3059501]
+	GetHandleVerifier [0x0x7ff628520bfd+3035885]
+	GetHandleVerifier [0x0x7ff6285403f0+3164896]
+	GetHandleVerifier [0x0x7ff628268c2e+185118]
+	GetHandleVerifier [0x0x7ff62827053f+216111]
+	GetHandleVerifier [0x0x7ff6282572d4+113092]
+	GetHandleVerifier [0x0x7ff628257489+113529]
+	GetHandleVerifier [0x0x7ff62823e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -2285,25 +2285,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c57e925+77845]
-	GetHandleVerifier [0x0x7ff61c57e980+77936]
-	(No symbol) [0x0x7ff61c339cda]
-	(No symbol) [0x0x7ff61c3906aa]
-	(No symbol) [0x0x7ff61c39095c]
-	(No symbol) [0x0x7ff61c3e3d07]
-	(No symbol) [0x0x7ff61c3b890f]
-	(No symbol) [0x0x7ff61c3e0b07]
-	(No symbol) [0x0x7ff61c3b86a3]
-	(No symbol) [0x0x7ff61c381791]
-	(No symbol) [0x0x7ff61c382523]
-	GetHandleVerifier [0x0x7ff61c85683d+3059501]
-	GetHandleVerifier [0x0x7ff61c850bfd+3035885]
-	GetHandleVerifier [0x0x7ff61c8703f0+3164896]
-	GetHandleVerifier [0x0x7ff61c598c2e+185118]
-	GetHandleVerifier [0x0x7ff61c5a053f+216111]
-	GetHandleVerifier [0x0x7ff61c5872d4+113092]
-	GetHandleVerifier [0x0x7ff61c587489+113529]
-	GetHandleVerifier [0x0x7ff61c56e288+10616]
+	GetHandleVerifier [0x0x7ff62824e925+77845]
+	GetHandleVerifier [0x0x7ff62824e980+77936]
+	(No symbol) [0x0x7ff628009cda]
+	(No symbol) [0x0x7ff6280606aa]
+	(No symbol) [0x0x7ff62806095c]
+	(No symbol) [0x0x7ff6280b3d07]
+	(No symbol) [0x0x7ff62808890f]
+	(No symbol) [0x0x7ff6280b0b07]
+	(No symbol) [0x0x7ff6280886a3]
+	(No symbol) [0x0x7ff628051791]
+	(No symbol) [0x0x7ff628052523]
+	GetHandleVerifier [0x0x7ff62852683d+3059501]
+	GetHandleVerifier [0x0x7ff628520bfd+3035885]
+	GetHandleVerifier [0x0x7ff6285403f0+3164896]
+	GetHandleVerifier [0x0x7ff628268c2e+185118]
+	GetHandleVerifier [0x0x7ff62827053f+216111]
+	GetHandleVerifier [0x0x7ff6282572d4+113092]
+	GetHandleVerifier [0x0x7ff628257489+113529]
+	GetHandleVerifier [0x0x7ff62823e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -2503,25 +2503,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c57e925+77845]
-	GetHandleVerifier [0x0x7ff61c57e980+77936]
-	(No symbol) [0x0x7ff61c339cda]
-	(No symbol) [0x0x7ff61c3906aa]
-	(No symbol) [0x0x7ff61c39095c]
-	(No symbol) [0x0x7ff61c3e3d07]
-	(No symbol) [0x0x7ff61c3b890f]
-	(No symbol) [0x0x7ff61c3e0b07]
-	(No symbol) [0x0x7ff61c3b86a3]
-	(No symbol) [0x0x7ff61c381791]
-	(No symbol) [0x0x7ff61c382523]
-	GetHandleVerifier [0x0x7ff61c85683d+3059501]
-	GetHandleVerifier [0x0x7ff61c850bfd+3035885]
-	GetHandleVerifier [0x0x7ff61c8703f0+3164896]
-	GetHandleVerifier [0x0x7ff61c598c2e+185118]
-	GetHandleVerifier [0x0x7ff61c5a053f+216111]
-	GetHandleVerifier [0x0x7ff61c5872d4+113092]
-	GetHandleVerifier [0x0x7ff61c587489+113529]
-	GetHandleVerifier [0x0x7ff61c56e288+10616]
+	GetHandleVerifier [0x0x7ff62824e925+77845]
+	GetHandleVerifier [0x0x7ff62824e980+77936]
+	(No symbol) [0x0x7ff628009cda]
+	(No symbol) [0x0x7ff6280606aa]
+	(No symbol) [0x0x7ff62806095c]
+	(No symbol) [0x0x7ff6280b3d07]
+	(No symbol) [0x0x7ff62808890f]
+	(No symbol) [0x0x7ff6280b0b07]
+	(No symbol) [0x0x7ff6280886a3]
+	(No symbol) [0x0x7ff628051791]
+	(No symbol) [0x0x7ff628052523]
+	GetHandleVerifier [0x0x7ff62852683d+3059501]
+	GetHandleVerifier [0x0x7ff628520bfd+3035885]
+	GetHandleVerifier [0x0x7ff6285403f0+3164896]
+	GetHandleVerifier [0x0x7ff628268c2e+185118]
+	GetHandleVerifier [0x0x7ff62827053f+216111]
+	GetHandleVerifier [0x0x7ff6282572d4+113092]
+	GetHandleVerifier [0x0x7ff628257489+113529]
+	GetHandleVerifier [0x0x7ff62823e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -2571,17 +2571,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>£29.40</t>
+          <t>£30.98</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>£29.40</t>
+          <t>£30.98</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>£29.40</t>
+          <t>£30.98</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2624,25 +2624,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c57e925+77845]
-	GetHandleVerifier [0x0x7ff61c57e980+77936]
-	(No symbol) [0x0x7ff61c339cda]
-	(No symbol) [0x0x7ff61c3906aa]
-	(No symbol) [0x0x7ff61c39095c]
-	(No symbol) [0x0x7ff61c3e3d07]
-	(No symbol) [0x0x7ff61c3b890f]
-	(No symbol) [0x0x7ff61c3e0b07]
-	(No symbol) [0x0x7ff61c3b86a3]
-	(No symbol) [0x0x7ff61c381791]
-	(No symbol) [0x0x7ff61c382523]
-	GetHandleVerifier [0x0x7ff61c85683d+3059501]
-	GetHandleVerifier [0x0x7ff61c850bfd+3035885]
-	GetHandleVerifier [0x0x7ff61c8703f0+3164896]
-	GetHandleVerifier [0x0x7ff61c598c2e+185118]
-	GetHandleVerifier [0x0x7ff61c5a053f+216111]
-	GetHandleVerifier [0x0x7ff61c5872d4+113092]
-	GetHandleVerifier [0x0x7ff61c587489+113529]
-	GetHandleVerifier [0x0x7ff61c56e288+10616]
+	GetHandleVerifier [0x0x7ff62824e925+77845]
+	GetHandleVerifier [0x0x7ff62824e980+77936]
+	(No symbol) [0x0x7ff628009cda]
+	(No symbol) [0x0x7ff6280606aa]
+	(No symbol) [0x0x7ff62806095c]
+	(No symbol) [0x0x7ff6280b3d07]
+	(No symbol) [0x0x7ff62808890f]
+	(No symbol) [0x0x7ff6280b0b07]
+	(No symbol) [0x0x7ff6280886a3]
+	(No symbol) [0x0x7ff628051791]
+	(No symbol) [0x0x7ff628052523]
+	GetHandleVerifier [0x0x7ff62852683d+3059501]
+	GetHandleVerifier [0x0x7ff628520bfd+3035885]
+	GetHandleVerifier [0x0x7ff6285403f0+3164896]
+	GetHandleVerifier [0x0x7ff628268c2e+185118]
+	GetHandleVerifier [0x0x7ff62827053f+216111]
+	GetHandleVerifier [0x0x7ff6282572d4+113092]
+	GetHandleVerifier [0x0x7ff628257489+113529]
+	GetHandleVerifier [0x0x7ff62823e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -2692,17 +2692,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>£36.20</t>
+          <t>£37.49</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>£36.20</t>
+          <t>£37.49</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>£36.20</t>
+          <t>£37.49</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2745,25 +2745,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c57e925+77845]
-	GetHandleVerifier [0x0x7ff61c57e980+77936]
-	(No symbol) [0x0x7ff61c339cda]
-	(No symbol) [0x0x7ff61c3906aa]
-	(No symbol) [0x0x7ff61c39095c]
-	(No symbol) [0x0x7ff61c3e3d07]
-	(No symbol) [0x0x7ff61c3b890f]
-	(No symbol) [0x0x7ff61c3e0b07]
-	(No symbol) [0x0x7ff61c3b86a3]
-	(No symbol) [0x0x7ff61c381791]
-	(No symbol) [0x0x7ff61c382523]
-	GetHandleVerifier [0x0x7ff61c85683d+3059501]
-	GetHandleVerifier [0x0x7ff61c850bfd+3035885]
-	GetHandleVerifier [0x0x7ff61c8703f0+3164896]
-	GetHandleVerifier [0x0x7ff61c598c2e+185118]
-	GetHandleVerifier [0x0x7ff61c5a053f+216111]
-	GetHandleVerifier [0x0x7ff61c5872d4+113092]
-	GetHandleVerifier [0x0x7ff61c587489+113529]
-	GetHandleVerifier [0x0x7ff61c56e288+10616]
+	GetHandleVerifier [0x0x7ff62824e925+77845]
+	GetHandleVerifier [0x0x7ff62824e980+77936]
+	(No symbol) [0x0x7ff628009cda]
+	(No symbol) [0x0x7ff6280606aa]
+	(No symbol) [0x0x7ff62806095c]
+	(No symbol) [0x0x7ff6280b3d07]
+	(No symbol) [0x0x7ff62808890f]
+	(No symbol) [0x0x7ff6280b0b07]
+	(No symbol) [0x0x7ff6280886a3]
+	(No symbol) [0x0x7ff628051791]
+	(No symbol) [0x0x7ff628052523]
+	GetHandleVerifier [0x0x7ff62852683d+3059501]
+	GetHandleVerifier [0x0x7ff628520bfd+3035885]
+	GetHandleVerifier [0x0x7ff6285403f0+3164896]
+	GetHandleVerifier [0x0x7ff628268c2e+185118]
+	GetHandleVerifier [0x0x7ff62827053f+216111]
+	GetHandleVerifier [0x0x7ff6282572d4+113092]
+	GetHandleVerifier [0x0x7ff628257489+113529]
+	GetHandleVerifier [0x0x7ff62823e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -2813,17 +2813,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>£40.21</t>
+          <t>£40.49</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>£40.21</t>
+          <t>£40.49</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>£33.35</t>
+          <t>£40.49</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2866,25 +2866,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c57e925+77845]
-	GetHandleVerifier [0x0x7ff61c57e980+77936]
-	(No symbol) [0x0x7ff61c339cda]
-	(No symbol) [0x0x7ff61c3906aa]
-	(No symbol) [0x0x7ff61c39095c]
-	(No symbol) [0x0x7ff61c3e3d07]
-	(No symbol) [0x0x7ff61c3b890f]
-	(No symbol) [0x0x7ff61c3e0b07]
-	(No symbol) [0x0x7ff61c3b86a3]
-	(No symbol) [0x0x7ff61c381791]
-	(No symbol) [0x0x7ff61c382523]
-	GetHandleVerifier [0x0x7ff61c85683d+3059501]
-	GetHandleVerifier [0x0x7ff61c850bfd+3035885]
-	GetHandleVerifier [0x0x7ff61c8703f0+3164896]
-	GetHandleVerifier [0x0x7ff61c598c2e+185118]
-	GetHandleVerifier [0x0x7ff61c5a053f+216111]
-	GetHandleVerifier [0x0x7ff61c5872d4+113092]
-	GetHandleVerifier [0x0x7ff61c587489+113529]
-	GetHandleVerifier [0x0x7ff61c56e288+10616]
+	GetHandleVerifier [0x0x7ff62824e925+77845]
+	GetHandleVerifier [0x0x7ff62824e980+77936]
+	(No symbol) [0x0x7ff628009cda]
+	(No symbol) [0x0x7ff6280606aa]
+	(No symbol) [0x0x7ff62806095c]
+	(No symbol) [0x0x7ff6280b3d07]
+	(No symbol) [0x0x7ff62808890f]
+	(No symbol) [0x0x7ff6280b0b07]
+	(No symbol) [0x0x7ff6280886a3]
+	(No symbol) [0x0x7ff628051791]
+	(No symbol) [0x0x7ff628052523]
+	GetHandleVerifier [0x0x7ff62852683d+3059501]
+	GetHandleVerifier [0x0x7ff628520bfd+3035885]
+	GetHandleVerifier [0x0x7ff6285403f0+3164896]
+	GetHandleVerifier [0x0x7ff628268c2e+185118]
+	GetHandleVerifier [0x0x7ff62827053f+216111]
+	GetHandleVerifier [0x0x7ff6282572d4+113092]
+	GetHandleVerifier [0x0x7ff628257489+113529]
+	GetHandleVerifier [0x0x7ff62823e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -2934,17 +2934,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>£43.89</t>
+          <t>£44.98</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>£43.89</t>
+          <t>£44.98</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>£43.89</t>
+          <t>£44.98</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2987,25 +2987,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c57e925+77845]
-	GetHandleVerifier [0x0x7ff61c57e980+77936]
-	(No symbol) [0x0x7ff61c339cda]
-	(No symbol) [0x0x7ff61c3906aa]
-	(No symbol) [0x0x7ff61c39095c]
-	(No symbol) [0x0x7ff61c3e3d07]
-	(No symbol) [0x0x7ff61c3b890f]
-	(No symbol) [0x0x7ff61c3e0b07]
-	(No symbol) [0x0x7ff61c3b86a3]
-	(No symbol) [0x0x7ff61c381791]
-	(No symbol) [0x0x7ff61c382523]
-	GetHandleVerifier [0x0x7ff61c85683d+3059501]
-	GetHandleVerifier [0x0x7ff61c850bfd+3035885]
-	GetHandleVerifier [0x0x7ff61c8703f0+3164896]
-	GetHandleVerifier [0x0x7ff61c598c2e+185118]
-	GetHandleVerifier [0x0x7ff61c5a053f+216111]
-	GetHandleVerifier [0x0x7ff61c5872d4+113092]
-	GetHandleVerifier [0x0x7ff61c587489+113529]
-	GetHandleVerifier [0x0x7ff61c56e288+10616]
+	GetHandleVerifier [0x0x7ff62824e925+77845]
+	GetHandleVerifier [0x0x7ff62824e980+77936]
+	(No symbol) [0x0x7ff628009cda]
+	(No symbol) [0x0x7ff6280606aa]
+	(No symbol) [0x0x7ff62806095c]
+	(No symbol) [0x0x7ff6280b3d07]
+	(No symbol) [0x0x7ff62808890f]
+	(No symbol) [0x0x7ff6280b0b07]
+	(No symbol) [0x0x7ff6280886a3]
+	(No symbol) [0x0x7ff628051791]
+	(No symbol) [0x0x7ff628052523]
+	GetHandleVerifier [0x0x7ff62852683d+3059501]
+	GetHandleVerifier [0x0x7ff628520bfd+3035885]
+	GetHandleVerifier [0x0x7ff6285403f0+3164896]
+	GetHandleVerifier [0x0x7ff628268c2e+185118]
+	GetHandleVerifier [0x0x7ff62827053f+216111]
+	GetHandleVerifier [0x0x7ff6282572d4+113092]
+	GetHandleVerifier [0x0x7ff628257489+113529]
+	GetHandleVerifier [0x0x7ff62823e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -3055,17 +3055,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>£44.60</t>
+          <t>£45.49</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>£44.60</t>
+          <t>£45.49</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>£44.60</t>
+          <t>£45.49</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -3108,25 +3108,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c57e925+77845]
-	GetHandleVerifier [0x0x7ff61c57e980+77936]
-	(No symbol) [0x0x7ff61c339cda]
-	(No symbol) [0x0x7ff61c3906aa]
-	(No symbol) [0x0x7ff61c39095c]
-	(No symbol) [0x0x7ff61c3e3d07]
-	(No symbol) [0x0x7ff61c3b890f]
-	(No symbol) [0x0x7ff61c3e0b07]
-	(No symbol) [0x0x7ff61c3b86a3]
-	(No symbol) [0x0x7ff61c381791]
-	(No symbol) [0x0x7ff61c382523]
-	GetHandleVerifier [0x0x7ff61c85683d+3059501]
-	GetHandleVerifier [0x0x7ff61c850bfd+3035885]
-	GetHandleVerifier [0x0x7ff61c8703f0+3164896]
-	GetHandleVerifier [0x0x7ff61c598c2e+185118]
-	GetHandleVerifier [0x0x7ff61c5a053f+216111]
-	GetHandleVerifier [0x0x7ff61c5872d4+113092]
-	GetHandleVerifier [0x0x7ff61c587489+113529]
-	GetHandleVerifier [0x0x7ff61c56e288+10616]
+	GetHandleVerifier [0x0x7ff62824e925+77845]
+	GetHandleVerifier [0x0x7ff62824e980+77936]
+	(No symbol) [0x0x7ff628009cda]
+	(No symbol) [0x0x7ff6280606aa]
+	(No symbol) [0x0x7ff62806095c]
+	(No symbol) [0x0x7ff6280b3d07]
+	(No symbol) [0x0x7ff62808890f]
+	(No symbol) [0x0x7ff6280b0b07]
+	(No symbol) [0x0x7ff6280886a3]
+	(No symbol) [0x0x7ff628051791]
+	(No symbol) [0x0x7ff628052523]
+	GetHandleVerifier [0x0x7ff62852683d+3059501]
+	GetHandleVerifier [0x0x7ff628520bfd+3035885]
+	GetHandleVerifier [0x0x7ff6285403f0+3164896]
+	GetHandleVerifier [0x0x7ff628268c2e+185118]
+	GetHandleVerifier [0x0x7ff62827053f+216111]
+	GetHandleVerifier [0x0x7ff6282572d4+113092]
+	GetHandleVerifier [0x0x7ff628257489+113529]
+	GetHandleVerifier [0x0x7ff62823e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -3176,17 +3176,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>£44.00</t>
+          <t>£43.99</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>£44.00</t>
+          <t>£43.99</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>£48.82</t>
+          <t>£43.99</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -3229,25 +3229,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c57e925+77845]
-	GetHandleVerifier [0x0x7ff61c57e980+77936]
-	(No symbol) [0x0x7ff61c339cda]
-	(No symbol) [0x0x7ff61c3906aa]
-	(No symbol) [0x0x7ff61c39095c]
-	(No symbol) [0x0x7ff61c3e3d07]
-	(No symbol) [0x0x7ff61c3b890f]
-	(No symbol) [0x0x7ff61c3e0b07]
-	(No symbol) [0x0x7ff61c3b86a3]
-	(No symbol) [0x0x7ff61c381791]
-	(No symbol) [0x0x7ff61c382523]
-	GetHandleVerifier [0x0x7ff61c85683d+3059501]
-	GetHandleVerifier [0x0x7ff61c850bfd+3035885]
-	GetHandleVerifier [0x0x7ff61c8703f0+3164896]
-	GetHandleVerifier [0x0x7ff61c598c2e+185118]
-	GetHandleVerifier [0x0x7ff61c5a053f+216111]
-	GetHandleVerifier [0x0x7ff61c5872d4+113092]
-	GetHandleVerifier [0x0x7ff61c587489+113529]
-	GetHandleVerifier [0x0x7ff61c56e288+10616]
+	GetHandleVerifier [0x0x7ff62824e925+77845]
+	GetHandleVerifier [0x0x7ff62824e980+77936]
+	(No symbol) [0x0x7ff628009cda]
+	(No symbol) [0x0x7ff6280606aa]
+	(No symbol) [0x0x7ff62806095c]
+	(No symbol) [0x0x7ff6280b3d07]
+	(No symbol) [0x0x7ff62808890f]
+	(No symbol) [0x0x7ff6280b0b07]
+	(No symbol) [0x0x7ff6280886a3]
+	(No symbol) [0x0x7ff628051791]
+	(No symbol) [0x0x7ff628052523]
+	GetHandleVerifier [0x0x7ff62852683d+3059501]
+	GetHandleVerifier [0x0x7ff628520bfd+3035885]
+	GetHandleVerifier [0x0x7ff6285403f0+3164896]
+	GetHandleVerifier [0x0x7ff628268c2e+185118]
+	GetHandleVerifier [0x0x7ff62827053f+216111]
+	GetHandleVerifier [0x0x7ff6282572d4+113092]
+	GetHandleVerifier [0x0x7ff628257489+113529]
+	GetHandleVerifier [0x0x7ff62823e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -3350,25 +3350,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c57e925+77845]
-	GetHandleVerifier [0x0x7ff61c57e980+77936]
-	(No symbol) [0x0x7ff61c339cda]
-	(No symbol) [0x0x7ff61c3906aa]
-	(No symbol) [0x0x7ff61c39095c]
-	(No symbol) [0x0x7ff61c3e3d07]
-	(No symbol) [0x0x7ff61c3b890f]
-	(No symbol) [0x0x7ff61c3e0b07]
-	(No symbol) [0x0x7ff61c3b86a3]
-	(No symbol) [0x0x7ff61c381791]
-	(No symbol) [0x0x7ff61c382523]
-	GetHandleVerifier [0x0x7ff61c85683d+3059501]
-	GetHandleVerifier [0x0x7ff61c850bfd+3035885]
-	GetHandleVerifier [0x0x7ff61c8703f0+3164896]
-	GetHandleVerifier [0x0x7ff61c598c2e+185118]
-	GetHandleVerifier [0x0x7ff61c5a053f+216111]
-	GetHandleVerifier [0x0x7ff61c5872d4+113092]
-	GetHandleVerifier [0x0x7ff61c587489+113529]
-	GetHandleVerifier [0x0x7ff61c56e288+10616]
+	GetHandleVerifier [0x0x7ff62824e925+77845]
+	GetHandleVerifier [0x0x7ff62824e980+77936]
+	(No symbol) [0x0x7ff628009cda]
+	(No symbol) [0x0x7ff6280606aa]
+	(No symbol) [0x0x7ff62806095c]
+	(No symbol) [0x0x7ff6280b3d07]
+	(No symbol) [0x0x7ff62808890f]
+	(No symbol) [0x0x7ff6280b0b07]
+	(No symbol) [0x0x7ff6280886a3]
+	(No symbol) [0x0x7ff628051791]
+	(No symbol) [0x0x7ff628052523]
+	GetHandleVerifier [0x0x7ff62852683d+3059501]
+	GetHandleVerifier [0x0x7ff628520bfd+3035885]
+	GetHandleVerifier [0x0x7ff6285403f0+3164896]
+	GetHandleVerifier [0x0x7ff628268c2e+185118]
+	GetHandleVerifier [0x0x7ff62827053f+216111]
+	GetHandleVerifier [0x0x7ff6282572d4+113092]
+	GetHandleVerifier [0x0x7ff628257489+113529]
+	GetHandleVerifier [0x0x7ff62823e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -3418,17 +3418,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>£44.20</t>
+          <t>£44.99</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>£44.20</t>
+          <t>£44.99</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>£44.20</t>
+          <t>£44.99</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3471,25 +3471,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c57e925+77845]
-	GetHandleVerifier [0x0x7ff61c57e980+77936]
-	(No symbol) [0x0x7ff61c339cda]
-	(No symbol) [0x0x7ff61c3906aa]
-	(No symbol) [0x0x7ff61c39095c]
-	(No symbol) [0x0x7ff61c3e3d07]
-	(No symbol) [0x0x7ff61c3b890f]
-	(No symbol) [0x0x7ff61c3e0b07]
-	(No symbol) [0x0x7ff61c3b86a3]
-	(No symbol) [0x0x7ff61c381791]
-	(No symbol) [0x0x7ff61c382523]
-	GetHandleVerifier [0x0x7ff61c85683d+3059501]
-	GetHandleVerifier [0x0x7ff61c850bfd+3035885]
-	GetHandleVerifier [0x0x7ff61c8703f0+3164896]
-	GetHandleVerifier [0x0x7ff61c598c2e+185118]
-	GetHandleVerifier [0x0x7ff61c5a053f+216111]
-	GetHandleVerifier [0x0x7ff61c5872d4+113092]
-	GetHandleVerifier [0x0x7ff61c587489+113529]
-	GetHandleVerifier [0x0x7ff61c56e288+10616]
+	GetHandleVerifier [0x0x7ff62824e925+77845]
+	GetHandleVerifier [0x0x7ff62824e980+77936]
+	(No symbol) [0x0x7ff628009cda]
+	(No symbol) [0x0x7ff6280606aa]
+	(No symbol) [0x0x7ff62806095c]
+	(No symbol) [0x0x7ff6280b3d07]
+	(No symbol) [0x0x7ff62808890f]
+	(No symbol) [0x0x7ff6280b0b07]
+	(No symbol) [0x0x7ff6280886a3]
+	(No symbol) [0x0x7ff628051791]
+	(No symbol) [0x0x7ff628052523]
+	GetHandleVerifier [0x0x7ff62852683d+3059501]
+	GetHandleVerifier [0x0x7ff628520bfd+3035885]
+	GetHandleVerifier [0x0x7ff6285403f0+3164896]
+	GetHandleVerifier [0x0x7ff628268c2e+185118]
+	GetHandleVerifier [0x0x7ff62827053f+216111]
+	GetHandleVerifier [0x0x7ff6282572d4+113092]
+	GetHandleVerifier [0x0x7ff628257489+113529]
+	GetHandleVerifier [0x0x7ff62823e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -3539,17 +3539,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>£1,160.00</t>
+          <t>£1,183.00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>£1,160.00</t>
+          <t>£1,183.00</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>£1,160.00</t>
+          <t>£1,183.00</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">

--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_18-07-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_18-07-2025.xlsx
@@ -591,25 +591,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff62824e925+77845]
-	GetHandleVerifier [0x0x7ff62824e980+77936]
-	(No symbol) [0x0x7ff628009cda]
-	(No symbol) [0x0x7ff6280606aa]
-	(No symbol) [0x0x7ff62806095c]
-	(No symbol) [0x0x7ff6280b3d07]
-	(No symbol) [0x0x7ff62808890f]
-	(No symbol) [0x0x7ff6280b0b07]
-	(No symbol) [0x0x7ff6280886a3]
-	(No symbol) [0x0x7ff628051791]
-	(No symbol) [0x0x7ff628052523]
-	GetHandleVerifier [0x0x7ff62852683d+3059501]
-	GetHandleVerifier [0x0x7ff628520bfd+3035885]
-	GetHandleVerifier [0x0x7ff6285403f0+3164896]
-	GetHandleVerifier [0x0x7ff628268c2e+185118]
-	GetHandleVerifier [0x0x7ff62827053f+216111]
-	GetHandleVerifier [0x0x7ff6282572d4+113092]
-	GetHandleVerifier [0x0x7ff628257489+113529]
-	GetHandleVerifier [0x0x7ff62823e288+10616]
+	GetHandleVerifier [0x0x7ff75762e925+77845]
+	GetHandleVerifier [0x0x7ff75762e980+77936]
+	(No symbol) [0x0x7ff7573e9cda]
+	(No symbol) [0x0x7ff7574406aa]
+	(No symbol) [0x0x7ff75744095c]
+	(No symbol) [0x0x7ff757493d07]
+	(No symbol) [0x0x7ff75746890f]
+	(No symbol) [0x0x7ff757490b07]
+	(No symbol) [0x0x7ff7574686a3]
+	(No symbol) [0x0x7ff757431791]
+	(No symbol) [0x0x7ff757432523]
+	GetHandleVerifier [0x0x7ff75790683d+3059501]
+	GetHandleVerifier [0x0x7ff757900bfd+3035885]
+	GetHandleVerifier [0x0x7ff7579203f0+3164896]
+	GetHandleVerifier [0x0x7ff757648c2e+185118]
+	GetHandleVerifier [0x0x7ff75765053f+216111]
+	GetHandleVerifier [0x0x7ff7576372d4+113092]
+	GetHandleVerifier [0x0x7ff757637489+113529]
+	GetHandleVerifier [0x0x7ff75761e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -712,25 +712,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff62824e925+77845]
-	GetHandleVerifier [0x0x7ff62824e980+77936]
-	(No symbol) [0x0x7ff628009cda]
-	(No symbol) [0x0x7ff6280606aa]
-	(No symbol) [0x0x7ff62806095c]
-	(No symbol) [0x0x7ff6280b3d07]
-	(No symbol) [0x0x7ff62808890f]
-	(No symbol) [0x0x7ff6280b0b07]
-	(No symbol) [0x0x7ff6280886a3]
-	(No symbol) [0x0x7ff628051791]
-	(No symbol) [0x0x7ff628052523]
-	GetHandleVerifier [0x0x7ff62852683d+3059501]
-	GetHandleVerifier [0x0x7ff628520bfd+3035885]
-	GetHandleVerifier [0x0x7ff6285403f0+3164896]
-	GetHandleVerifier [0x0x7ff628268c2e+185118]
-	GetHandleVerifier [0x0x7ff62827053f+216111]
-	GetHandleVerifier [0x0x7ff6282572d4+113092]
-	GetHandleVerifier [0x0x7ff628257489+113529]
-	GetHandleVerifier [0x0x7ff62823e288+10616]
+	GetHandleVerifier [0x0x7ff75762e925+77845]
+	GetHandleVerifier [0x0x7ff75762e980+77936]
+	(No symbol) [0x0x7ff7573e9cda]
+	(No symbol) [0x0x7ff7574406aa]
+	(No symbol) [0x0x7ff75744095c]
+	(No symbol) [0x0x7ff757493d07]
+	(No symbol) [0x0x7ff75746890f]
+	(No symbol) [0x0x7ff757490b07]
+	(No symbol) [0x0x7ff7574686a3]
+	(No symbol) [0x0x7ff757431791]
+	(No symbol) [0x0x7ff757432523]
+	GetHandleVerifier [0x0x7ff75790683d+3059501]
+	GetHandleVerifier [0x0x7ff757900bfd+3035885]
+	GetHandleVerifier [0x0x7ff7579203f0+3164896]
+	GetHandleVerifier [0x0x7ff757648c2e+185118]
+	GetHandleVerifier [0x0x7ff75765053f+216111]
+	GetHandleVerifier [0x0x7ff7576372d4+113092]
+	GetHandleVerifier [0x0x7ff757637489+113529]
+	GetHandleVerifier [0x0x7ff75761e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -833,25 +833,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff62824e925+77845]
-	GetHandleVerifier [0x0x7ff62824e980+77936]
-	(No symbol) [0x0x7ff628009cda]
-	(No symbol) [0x0x7ff6280606aa]
-	(No symbol) [0x0x7ff62806095c]
-	(No symbol) [0x0x7ff6280b3d07]
-	(No symbol) [0x0x7ff62808890f]
-	(No symbol) [0x0x7ff6280b0b07]
-	(No symbol) [0x0x7ff6280886a3]
-	(No symbol) [0x0x7ff628051791]
-	(No symbol) [0x0x7ff628052523]
-	GetHandleVerifier [0x0x7ff62852683d+3059501]
-	GetHandleVerifier [0x0x7ff628520bfd+3035885]
-	GetHandleVerifier [0x0x7ff6285403f0+3164896]
-	GetHandleVerifier [0x0x7ff628268c2e+185118]
-	GetHandleVerifier [0x0x7ff62827053f+216111]
-	GetHandleVerifier [0x0x7ff6282572d4+113092]
-	GetHandleVerifier [0x0x7ff628257489+113529]
-	GetHandleVerifier [0x0x7ff62823e288+10616]
+	GetHandleVerifier [0x0x7ff75762e925+77845]
+	GetHandleVerifier [0x0x7ff75762e980+77936]
+	(No symbol) [0x0x7ff7573e9cda]
+	(No symbol) [0x0x7ff7574406aa]
+	(No symbol) [0x0x7ff75744095c]
+	(No symbol) [0x0x7ff757493d07]
+	(No symbol) [0x0x7ff75746890f]
+	(No symbol) [0x0x7ff757490b07]
+	(No symbol) [0x0x7ff7574686a3]
+	(No symbol) [0x0x7ff757431791]
+	(No symbol) [0x0x7ff757432523]
+	GetHandleVerifier [0x0x7ff75790683d+3059501]
+	GetHandleVerifier [0x0x7ff757900bfd+3035885]
+	GetHandleVerifier [0x0x7ff7579203f0+3164896]
+	GetHandleVerifier [0x0x7ff757648c2e+185118]
+	GetHandleVerifier [0x0x7ff75765053f+216111]
+	GetHandleVerifier [0x0x7ff7576372d4+113092]
+	GetHandleVerifier [0x0x7ff757637489+113529]
+	GetHandleVerifier [0x0x7ff75761e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -954,25 +954,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff62824e925+77845]
-	GetHandleVerifier [0x0x7ff62824e980+77936]
-	(No symbol) [0x0x7ff628009cda]
-	(No symbol) [0x0x7ff6280606aa]
-	(No symbol) [0x0x7ff62806095c]
-	(No symbol) [0x0x7ff6280b3d07]
-	(No symbol) [0x0x7ff62808890f]
-	(No symbol) [0x0x7ff6280b0b07]
-	(No symbol) [0x0x7ff6280886a3]
-	(No symbol) [0x0x7ff628051791]
-	(No symbol) [0x0x7ff628052523]
-	GetHandleVerifier [0x0x7ff62852683d+3059501]
-	GetHandleVerifier [0x0x7ff628520bfd+3035885]
-	GetHandleVerifier [0x0x7ff6285403f0+3164896]
-	GetHandleVerifier [0x0x7ff628268c2e+185118]
-	GetHandleVerifier [0x0x7ff62827053f+216111]
-	GetHandleVerifier [0x0x7ff6282572d4+113092]
-	GetHandleVerifier [0x0x7ff628257489+113529]
-	GetHandleVerifier [0x0x7ff62823e288+10616]
+	GetHandleVerifier [0x0x7ff75762e925+77845]
+	GetHandleVerifier [0x0x7ff75762e980+77936]
+	(No symbol) [0x0x7ff7573e9cda]
+	(No symbol) [0x0x7ff7574406aa]
+	(No symbol) [0x0x7ff75744095c]
+	(No symbol) [0x0x7ff757493d07]
+	(No symbol) [0x0x7ff75746890f]
+	(No symbol) [0x0x7ff757490b07]
+	(No symbol) [0x0x7ff7574686a3]
+	(No symbol) [0x0x7ff757431791]
+	(No symbol) [0x0x7ff757432523]
+	GetHandleVerifier [0x0x7ff75790683d+3059501]
+	GetHandleVerifier [0x0x7ff757900bfd+3035885]
+	GetHandleVerifier [0x0x7ff7579203f0+3164896]
+	GetHandleVerifier [0x0x7ff757648c2e+185118]
+	GetHandleVerifier [0x0x7ff75765053f+216111]
+	GetHandleVerifier [0x0x7ff7576372d4+113092]
+	GetHandleVerifier [0x0x7ff757637489+113529]
+	GetHandleVerifier [0x0x7ff75761e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -1075,25 +1075,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff62824e925+77845]
-	GetHandleVerifier [0x0x7ff62824e980+77936]
-	(No symbol) [0x0x7ff628009cda]
-	(No symbol) [0x0x7ff6280606aa]
-	(No symbol) [0x0x7ff62806095c]
-	(No symbol) [0x0x7ff6280b3d07]
-	(No symbol) [0x0x7ff62808890f]
-	(No symbol) [0x0x7ff6280b0b07]
-	(No symbol) [0x0x7ff6280886a3]
-	(No symbol) [0x0x7ff628051791]
-	(No symbol) [0x0x7ff628052523]
-	GetHandleVerifier [0x0x7ff62852683d+3059501]
-	GetHandleVerifier [0x0x7ff628520bfd+3035885]
-	GetHandleVerifier [0x0x7ff6285403f0+3164896]
-	GetHandleVerifier [0x0x7ff628268c2e+185118]
-	GetHandleVerifier [0x0x7ff62827053f+216111]
-	GetHandleVerifier [0x0x7ff6282572d4+113092]
-	GetHandleVerifier [0x0x7ff628257489+113529]
-	GetHandleVerifier [0x0x7ff62823e288+10616]
+	GetHandleVerifier [0x0x7ff75762e925+77845]
+	GetHandleVerifier [0x0x7ff75762e980+77936]
+	(No symbol) [0x0x7ff7573e9cda]
+	(No symbol) [0x0x7ff7574406aa]
+	(No symbol) [0x0x7ff75744095c]
+	(No symbol) [0x0x7ff757493d07]
+	(No symbol) [0x0x7ff75746890f]
+	(No symbol) [0x0x7ff757490b07]
+	(No symbol) [0x0x7ff7574686a3]
+	(No symbol) [0x0x7ff757431791]
+	(No symbol) [0x0x7ff757432523]
+	GetHandleVerifier [0x0x7ff75790683d+3059501]
+	GetHandleVerifier [0x0x7ff757900bfd+3035885]
+	GetHandleVerifier [0x0x7ff7579203f0+3164896]
+	GetHandleVerifier [0x0x7ff757648c2e+185118]
+	GetHandleVerifier [0x0x7ff75765053f+216111]
+	GetHandleVerifier [0x0x7ff7576372d4+113092]
+	GetHandleVerifier [0x0x7ff757637489+113529]
+	GetHandleVerifier [0x0x7ff75761e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -1196,25 +1196,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff62824e925+77845]
-	GetHandleVerifier [0x0x7ff62824e980+77936]
-	(No symbol) [0x0x7ff628009cda]
-	(No symbol) [0x0x7ff6280606aa]
-	(No symbol) [0x0x7ff62806095c]
-	(No symbol) [0x0x7ff6280b3d07]
-	(No symbol) [0x0x7ff62808890f]
-	(No symbol) [0x0x7ff6280b0b07]
-	(No symbol) [0x0x7ff6280886a3]
-	(No symbol) [0x0x7ff628051791]
-	(No symbol) [0x0x7ff628052523]
-	GetHandleVerifier [0x0x7ff62852683d+3059501]
-	GetHandleVerifier [0x0x7ff628520bfd+3035885]
-	GetHandleVerifier [0x0x7ff6285403f0+3164896]
-	GetHandleVerifier [0x0x7ff628268c2e+185118]
-	GetHandleVerifier [0x0x7ff62827053f+216111]
-	GetHandleVerifier [0x0x7ff6282572d4+113092]
-	GetHandleVerifier [0x0x7ff628257489+113529]
-	GetHandleVerifier [0x0x7ff62823e288+10616]
+	GetHandleVerifier [0x0x7ff75762e925+77845]
+	GetHandleVerifier [0x0x7ff75762e980+77936]
+	(No symbol) [0x0x7ff7573e9cda]
+	(No symbol) [0x0x7ff7574406aa]
+	(No symbol) [0x0x7ff75744095c]
+	(No symbol) [0x0x7ff757493d07]
+	(No symbol) [0x0x7ff75746890f]
+	(No symbol) [0x0x7ff757490b07]
+	(No symbol) [0x0x7ff7574686a3]
+	(No symbol) [0x0x7ff757431791]
+	(No symbol) [0x0x7ff757432523]
+	GetHandleVerifier [0x0x7ff75790683d+3059501]
+	GetHandleVerifier [0x0x7ff757900bfd+3035885]
+	GetHandleVerifier [0x0x7ff7579203f0+3164896]
+	GetHandleVerifier [0x0x7ff757648c2e+185118]
+	GetHandleVerifier [0x0x7ff75765053f+216111]
+	GetHandleVerifier [0x0x7ff7576372d4+113092]
+	GetHandleVerifier [0x0x7ff757637489+113529]
+	GetHandleVerifier [0x0x7ff75761e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -1317,25 +1317,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff62824e925+77845]
-	GetHandleVerifier [0x0x7ff62824e980+77936]
-	(No symbol) [0x0x7ff628009cda]
-	(No symbol) [0x0x7ff6280606aa]
-	(No symbol) [0x0x7ff62806095c]
-	(No symbol) [0x0x7ff6280b3d07]
-	(No symbol) [0x0x7ff62808890f]
-	(No symbol) [0x0x7ff6280b0b07]
-	(No symbol) [0x0x7ff6280886a3]
-	(No symbol) [0x0x7ff628051791]
-	(No symbol) [0x0x7ff628052523]
-	GetHandleVerifier [0x0x7ff62852683d+3059501]
-	GetHandleVerifier [0x0x7ff628520bfd+3035885]
-	GetHandleVerifier [0x0x7ff6285403f0+3164896]
-	GetHandleVerifier [0x0x7ff628268c2e+185118]
-	GetHandleVerifier [0x0x7ff62827053f+216111]
-	GetHandleVerifier [0x0x7ff6282572d4+113092]
-	GetHandleVerifier [0x0x7ff628257489+113529]
-	GetHandleVerifier [0x0x7ff62823e288+10616]
+	GetHandleVerifier [0x0x7ff75762e925+77845]
+	GetHandleVerifier [0x0x7ff75762e980+77936]
+	(No symbol) [0x0x7ff7573e9cda]
+	(No symbol) [0x0x7ff7574406aa]
+	(No symbol) [0x0x7ff75744095c]
+	(No symbol) [0x0x7ff757493d07]
+	(No symbol) [0x0x7ff75746890f]
+	(No symbol) [0x0x7ff757490b07]
+	(No symbol) [0x0x7ff7574686a3]
+	(No symbol) [0x0x7ff757431791]
+	(No symbol) [0x0x7ff757432523]
+	GetHandleVerifier [0x0x7ff75790683d+3059501]
+	GetHandleVerifier [0x0x7ff757900bfd+3035885]
+	GetHandleVerifier [0x0x7ff7579203f0+3164896]
+	GetHandleVerifier [0x0x7ff757648c2e+185118]
+	GetHandleVerifier [0x0x7ff75765053f+216111]
+	GetHandleVerifier [0x0x7ff7576372d4+113092]
+	GetHandleVerifier [0x0x7ff757637489+113529]
+	GetHandleVerifier [0x0x7ff75761e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -1438,25 +1438,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff62824e925+77845]
-	GetHandleVerifier [0x0x7ff62824e980+77936]
-	(No symbol) [0x0x7ff628009cda]
-	(No symbol) [0x0x7ff6280606aa]
-	(No symbol) [0x0x7ff62806095c]
-	(No symbol) [0x0x7ff6280b3d07]
-	(No symbol) [0x0x7ff62808890f]
-	(No symbol) [0x0x7ff6280b0b07]
-	(No symbol) [0x0x7ff6280886a3]
-	(No symbol) [0x0x7ff628051791]
-	(No symbol) [0x0x7ff628052523]
-	GetHandleVerifier [0x0x7ff62852683d+3059501]
-	GetHandleVerifier [0x0x7ff628520bfd+3035885]
-	GetHandleVerifier [0x0x7ff6285403f0+3164896]
-	GetHandleVerifier [0x0x7ff628268c2e+185118]
-	GetHandleVerifier [0x0x7ff62827053f+216111]
-	GetHandleVerifier [0x0x7ff6282572d4+113092]
-	GetHandleVerifier [0x0x7ff628257489+113529]
-	GetHandleVerifier [0x0x7ff62823e288+10616]
+	GetHandleVerifier [0x0x7ff75762e925+77845]
+	GetHandleVerifier [0x0x7ff75762e980+77936]
+	(No symbol) [0x0x7ff7573e9cda]
+	(No symbol) [0x0x7ff7574406aa]
+	(No symbol) [0x0x7ff75744095c]
+	(No symbol) [0x0x7ff757493d07]
+	(No symbol) [0x0x7ff75746890f]
+	(No symbol) [0x0x7ff757490b07]
+	(No symbol) [0x0x7ff7574686a3]
+	(No symbol) [0x0x7ff757431791]
+	(No symbol) [0x0x7ff757432523]
+	GetHandleVerifier [0x0x7ff75790683d+3059501]
+	GetHandleVerifier [0x0x7ff757900bfd+3035885]
+	GetHandleVerifier [0x0x7ff7579203f0+3164896]
+	GetHandleVerifier [0x0x7ff757648c2e+185118]
+	GetHandleVerifier [0x0x7ff75765053f+216111]
+	GetHandleVerifier [0x0x7ff7576372d4+113092]
+	GetHandleVerifier [0x0x7ff757637489+113529]
+	GetHandleVerifier [0x0x7ff75761e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -1559,25 +1559,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff62824e925+77845]
-	GetHandleVerifier [0x0x7ff62824e980+77936]
-	(No symbol) [0x0x7ff628009cda]
-	(No symbol) [0x0x7ff6280606aa]
-	(No symbol) [0x0x7ff62806095c]
-	(No symbol) [0x0x7ff6280b3d07]
-	(No symbol) [0x0x7ff62808890f]
-	(No symbol) [0x0x7ff6280b0b07]
-	(No symbol) [0x0x7ff6280886a3]
-	(No symbol) [0x0x7ff628051791]
-	(No symbol) [0x0x7ff628052523]
-	GetHandleVerifier [0x0x7ff62852683d+3059501]
-	GetHandleVerifier [0x0x7ff628520bfd+3035885]
-	GetHandleVerifier [0x0x7ff6285403f0+3164896]
-	GetHandleVerifier [0x0x7ff628268c2e+185118]
-	GetHandleVerifier [0x0x7ff62827053f+216111]
-	GetHandleVerifier [0x0x7ff6282572d4+113092]
-	GetHandleVerifier [0x0x7ff628257489+113529]
-	GetHandleVerifier [0x0x7ff62823e288+10616]
+	GetHandleVerifier [0x0x7ff75762e925+77845]
+	GetHandleVerifier [0x0x7ff75762e980+77936]
+	(No symbol) [0x0x7ff7573e9cda]
+	(No symbol) [0x0x7ff7574406aa]
+	(No symbol) [0x0x7ff75744095c]
+	(No symbol) [0x0x7ff757493d07]
+	(No symbol) [0x0x7ff75746890f]
+	(No symbol) [0x0x7ff757490b07]
+	(No symbol) [0x0x7ff7574686a3]
+	(No symbol) [0x0x7ff757431791]
+	(No symbol) [0x0x7ff757432523]
+	GetHandleVerifier [0x0x7ff75790683d+3059501]
+	GetHandleVerifier [0x0x7ff757900bfd+3035885]
+	GetHandleVerifier [0x0x7ff7579203f0+3164896]
+	GetHandleVerifier [0x0x7ff757648c2e+185118]
+	GetHandleVerifier [0x0x7ff75765053f+216111]
+	GetHandleVerifier [0x0x7ff7576372d4+113092]
+	GetHandleVerifier [0x0x7ff757637489+113529]
+	GetHandleVerifier [0x0x7ff75761e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -1680,25 +1680,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff62824e925+77845]
-	GetHandleVerifier [0x0x7ff62824e980+77936]
-	(No symbol) [0x0x7ff628009cda]
-	(No symbol) [0x0x7ff6280606aa]
-	(No symbol) [0x0x7ff62806095c]
-	(No symbol) [0x0x7ff6280b3d07]
-	(No symbol) [0x0x7ff62808890f]
-	(No symbol) [0x0x7ff6280b0b07]
-	(No symbol) [0x0x7ff6280886a3]
-	(No symbol) [0x0x7ff628051791]
-	(No symbol) [0x0x7ff628052523]
-	GetHandleVerifier [0x0x7ff62852683d+3059501]
-	GetHandleVerifier [0x0x7ff628520bfd+3035885]
-	GetHandleVerifier [0x0x7ff6285403f0+3164896]
-	GetHandleVerifier [0x0x7ff628268c2e+185118]
-	GetHandleVerifier [0x0x7ff62827053f+216111]
-	GetHandleVerifier [0x0x7ff6282572d4+113092]
-	GetHandleVerifier [0x0x7ff628257489+113529]
-	GetHandleVerifier [0x0x7ff62823e288+10616]
+	GetHandleVerifier [0x0x7ff75762e925+77845]
+	GetHandleVerifier [0x0x7ff75762e980+77936]
+	(No symbol) [0x0x7ff7573e9cda]
+	(No symbol) [0x0x7ff7574406aa]
+	(No symbol) [0x0x7ff75744095c]
+	(No symbol) [0x0x7ff757493d07]
+	(No symbol) [0x0x7ff75746890f]
+	(No symbol) [0x0x7ff757490b07]
+	(No symbol) [0x0x7ff7574686a3]
+	(No symbol) [0x0x7ff757431791]
+	(No symbol) [0x0x7ff757432523]
+	GetHandleVerifier [0x0x7ff75790683d+3059501]
+	GetHandleVerifier [0x0x7ff757900bfd+3035885]
+	GetHandleVerifier [0x0x7ff7579203f0+3164896]
+	GetHandleVerifier [0x0x7ff757648c2e+185118]
+	GetHandleVerifier [0x0x7ff75765053f+216111]
+	GetHandleVerifier [0x0x7ff7576372d4+113092]
+	GetHandleVerifier [0x0x7ff757637489+113529]
+	GetHandleVerifier [0x0x7ff75761e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -1801,25 +1801,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff62824e925+77845]
-	GetHandleVerifier [0x0x7ff62824e980+77936]
-	(No symbol) [0x0x7ff628009cda]
-	(No symbol) [0x0x7ff6280606aa]
-	(No symbol) [0x0x7ff62806095c]
-	(No symbol) [0x0x7ff6280b3d07]
-	(No symbol) [0x0x7ff62808890f]
-	(No symbol) [0x0x7ff6280b0b07]
-	(No symbol) [0x0x7ff6280886a3]
-	(No symbol) [0x0x7ff628051791]
-	(No symbol) [0x0x7ff628052523]
-	GetHandleVerifier [0x0x7ff62852683d+3059501]
-	GetHandleVerifier [0x0x7ff628520bfd+3035885]
-	GetHandleVerifier [0x0x7ff6285403f0+3164896]
-	GetHandleVerifier [0x0x7ff628268c2e+185118]
-	GetHandleVerifier [0x0x7ff62827053f+216111]
-	GetHandleVerifier [0x0x7ff6282572d4+113092]
-	GetHandleVerifier [0x0x7ff628257489+113529]
-	GetHandleVerifier [0x0x7ff62823e288+10616]
+	GetHandleVerifier [0x0x7ff75762e925+77845]
+	GetHandleVerifier [0x0x7ff75762e980+77936]
+	(No symbol) [0x0x7ff7573e9cda]
+	(No symbol) [0x0x7ff7574406aa]
+	(No symbol) [0x0x7ff75744095c]
+	(No symbol) [0x0x7ff757493d07]
+	(No symbol) [0x0x7ff75746890f]
+	(No symbol) [0x0x7ff757490b07]
+	(No symbol) [0x0x7ff7574686a3]
+	(No symbol) [0x0x7ff757431791]
+	(No symbol) [0x0x7ff757432523]
+	GetHandleVerifier [0x0x7ff75790683d+3059501]
+	GetHandleVerifier [0x0x7ff757900bfd+3035885]
+	GetHandleVerifier [0x0x7ff7579203f0+3164896]
+	GetHandleVerifier [0x0x7ff757648c2e+185118]
+	GetHandleVerifier [0x0x7ff75765053f+216111]
+	GetHandleVerifier [0x0x7ff7576372d4+113092]
+	GetHandleVerifier [0x0x7ff757637489+113529]
+	GetHandleVerifier [0x0x7ff75761e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -1922,25 +1922,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff62824e925+77845]
-	GetHandleVerifier [0x0x7ff62824e980+77936]
-	(No symbol) [0x0x7ff628009cda]
-	(No symbol) [0x0x7ff6280606aa]
-	(No symbol) [0x0x7ff62806095c]
-	(No symbol) [0x0x7ff6280b3d07]
-	(No symbol) [0x0x7ff62808890f]
-	(No symbol) [0x0x7ff6280b0b07]
-	(No symbol) [0x0x7ff6280886a3]
-	(No symbol) [0x0x7ff628051791]
-	(No symbol) [0x0x7ff628052523]
-	GetHandleVerifier [0x0x7ff62852683d+3059501]
-	GetHandleVerifier [0x0x7ff628520bfd+3035885]
-	GetHandleVerifier [0x0x7ff6285403f0+3164896]
-	GetHandleVerifier [0x0x7ff628268c2e+185118]
-	GetHandleVerifier [0x0x7ff62827053f+216111]
-	GetHandleVerifier [0x0x7ff6282572d4+113092]
-	GetHandleVerifier [0x0x7ff628257489+113529]
-	GetHandleVerifier [0x0x7ff62823e288+10616]
+	GetHandleVerifier [0x0x7ff75762e925+77845]
+	GetHandleVerifier [0x0x7ff75762e980+77936]
+	(No symbol) [0x0x7ff7573e9cda]
+	(No symbol) [0x0x7ff7574406aa]
+	(No symbol) [0x0x7ff75744095c]
+	(No symbol) [0x0x7ff757493d07]
+	(No symbol) [0x0x7ff75746890f]
+	(No symbol) [0x0x7ff757490b07]
+	(No symbol) [0x0x7ff7574686a3]
+	(No symbol) [0x0x7ff757431791]
+	(No symbol) [0x0x7ff757432523]
+	GetHandleVerifier [0x0x7ff75790683d+3059501]
+	GetHandleVerifier [0x0x7ff757900bfd+3035885]
+	GetHandleVerifier [0x0x7ff7579203f0+3164896]
+	GetHandleVerifier [0x0x7ff757648c2e+185118]
+	GetHandleVerifier [0x0x7ff75765053f+216111]
+	GetHandleVerifier [0x0x7ff7576372d4+113092]
+	GetHandleVerifier [0x0x7ff757637489+113529]
+	GetHandleVerifier [0x0x7ff75761e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -2043,25 +2043,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff62824e925+77845]
-	GetHandleVerifier [0x0x7ff62824e980+77936]
-	(No symbol) [0x0x7ff628009cda]
-	(No symbol) [0x0x7ff6280606aa]
-	(No symbol) [0x0x7ff62806095c]
-	(No symbol) [0x0x7ff6280b3d07]
-	(No symbol) [0x0x7ff62808890f]
-	(No symbol) [0x0x7ff6280b0b07]
-	(No symbol) [0x0x7ff6280886a3]
-	(No symbol) [0x0x7ff628051791]
-	(No symbol) [0x0x7ff628052523]
-	GetHandleVerifier [0x0x7ff62852683d+3059501]
-	GetHandleVerifier [0x0x7ff628520bfd+3035885]
-	GetHandleVerifier [0x0x7ff6285403f0+3164896]
-	GetHandleVerifier [0x0x7ff628268c2e+185118]
-	GetHandleVerifier [0x0x7ff62827053f+216111]
-	GetHandleVerifier [0x0x7ff6282572d4+113092]
-	GetHandleVerifier [0x0x7ff628257489+113529]
-	GetHandleVerifier [0x0x7ff62823e288+10616]
+	GetHandleVerifier [0x0x7ff75762e925+77845]
+	GetHandleVerifier [0x0x7ff75762e980+77936]
+	(No symbol) [0x0x7ff7573e9cda]
+	(No symbol) [0x0x7ff7574406aa]
+	(No symbol) [0x0x7ff75744095c]
+	(No symbol) [0x0x7ff757493d07]
+	(No symbol) [0x0x7ff75746890f]
+	(No symbol) [0x0x7ff757490b07]
+	(No symbol) [0x0x7ff7574686a3]
+	(No symbol) [0x0x7ff757431791]
+	(No symbol) [0x0x7ff757432523]
+	GetHandleVerifier [0x0x7ff75790683d+3059501]
+	GetHandleVerifier [0x0x7ff757900bfd+3035885]
+	GetHandleVerifier [0x0x7ff7579203f0+3164896]
+	GetHandleVerifier [0x0x7ff757648c2e+185118]
+	GetHandleVerifier [0x0x7ff75765053f+216111]
+	GetHandleVerifier [0x0x7ff7576372d4+113092]
+	GetHandleVerifier [0x0x7ff757637489+113529]
+	GetHandleVerifier [0x0x7ff75761e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -2164,25 +2164,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff62824e925+77845]
-	GetHandleVerifier [0x0x7ff62824e980+77936]
-	(No symbol) [0x0x7ff628009cda]
-	(No symbol) [0x0x7ff6280606aa]
-	(No symbol) [0x0x7ff62806095c]
-	(No symbol) [0x0x7ff6280b3d07]
-	(No symbol) [0x0x7ff62808890f]
-	(No symbol) [0x0x7ff6280b0b07]
-	(No symbol) [0x0x7ff6280886a3]
-	(No symbol) [0x0x7ff628051791]
-	(No symbol) [0x0x7ff628052523]
-	GetHandleVerifier [0x0x7ff62852683d+3059501]
-	GetHandleVerifier [0x0x7ff628520bfd+3035885]
-	GetHandleVerifier [0x0x7ff6285403f0+3164896]
-	GetHandleVerifier [0x0x7ff628268c2e+185118]
-	GetHandleVerifier [0x0x7ff62827053f+216111]
-	GetHandleVerifier [0x0x7ff6282572d4+113092]
-	GetHandleVerifier [0x0x7ff628257489+113529]
-	GetHandleVerifier [0x0x7ff62823e288+10616]
+	GetHandleVerifier [0x0x7ff75762e925+77845]
+	GetHandleVerifier [0x0x7ff75762e980+77936]
+	(No symbol) [0x0x7ff7573e9cda]
+	(No symbol) [0x0x7ff7574406aa]
+	(No symbol) [0x0x7ff75744095c]
+	(No symbol) [0x0x7ff757493d07]
+	(No symbol) [0x0x7ff75746890f]
+	(No symbol) [0x0x7ff757490b07]
+	(No symbol) [0x0x7ff7574686a3]
+	(No symbol) [0x0x7ff757431791]
+	(No symbol) [0x0x7ff757432523]
+	GetHandleVerifier [0x0x7ff75790683d+3059501]
+	GetHandleVerifier [0x0x7ff757900bfd+3035885]
+	GetHandleVerifier [0x0x7ff7579203f0+3164896]
+	GetHandleVerifier [0x0x7ff757648c2e+185118]
+	GetHandleVerifier [0x0x7ff75765053f+216111]
+	GetHandleVerifier [0x0x7ff7576372d4+113092]
+	GetHandleVerifier [0x0x7ff757637489+113529]
+	GetHandleVerifier [0x0x7ff75761e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -2285,25 +2285,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff62824e925+77845]
-	GetHandleVerifier [0x0x7ff62824e980+77936]
-	(No symbol) [0x0x7ff628009cda]
-	(No symbol) [0x0x7ff6280606aa]
-	(No symbol) [0x0x7ff62806095c]
-	(No symbol) [0x0x7ff6280b3d07]
-	(No symbol) [0x0x7ff62808890f]
-	(No symbol) [0x0x7ff6280b0b07]
-	(No symbol) [0x0x7ff6280886a3]
-	(No symbol) [0x0x7ff628051791]
-	(No symbol) [0x0x7ff628052523]
-	GetHandleVerifier [0x0x7ff62852683d+3059501]
-	GetHandleVerifier [0x0x7ff628520bfd+3035885]
-	GetHandleVerifier [0x0x7ff6285403f0+3164896]
-	GetHandleVerifier [0x0x7ff628268c2e+185118]
-	GetHandleVerifier [0x0x7ff62827053f+216111]
-	GetHandleVerifier [0x0x7ff6282572d4+113092]
-	GetHandleVerifier [0x0x7ff628257489+113529]
-	GetHandleVerifier [0x0x7ff62823e288+10616]
+	GetHandleVerifier [0x0x7ff75762e925+77845]
+	GetHandleVerifier [0x0x7ff75762e980+77936]
+	(No symbol) [0x0x7ff7573e9cda]
+	(No symbol) [0x0x7ff7574406aa]
+	(No symbol) [0x0x7ff75744095c]
+	(No symbol) [0x0x7ff757493d07]
+	(No symbol) [0x0x7ff75746890f]
+	(No symbol) [0x0x7ff757490b07]
+	(No symbol) [0x0x7ff7574686a3]
+	(No symbol) [0x0x7ff757431791]
+	(No symbol) [0x0x7ff757432523]
+	GetHandleVerifier [0x0x7ff75790683d+3059501]
+	GetHandleVerifier [0x0x7ff757900bfd+3035885]
+	GetHandleVerifier [0x0x7ff7579203f0+3164896]
+	GetHandleVerifier [0x0x7ff757648c2e+185118]
+	GetHandleVerifier [0x0x7ff75765053f+216111]
+	GetHandleVerifier [0x0x7ff7576372d4+113092]
+	GetHandleVerifier [0x0x7ff757637489+113529]
+	GetHandleVerifier [0x0x7ff75761e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -2503,25 +2503,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff62824e925+77845]
-	GetHandleVerifier [0x0x7ff62824e980+77936]
-	(No symbol) [0x0x7ff628009cda]
-	(No symbol) [0x0x7ff6280606aa]
-	(No symbol) [0x0x7ff62806095c]
-	(No symbol) [0x0x7ff6280b3d07]
-	(No symbol) [0x0x7ff62808890f]
-	(No symbol) [0x0x7ff6280b0b07]
-	(No symbol) [0x0x7ff6280886a3]
-	(No symbol) [0x0x7ff628051791]
-	(No symbol) [0x0x7ff628052523]
-	GetHandleVerifier [0x0x7ff62852683d+3059501]
-	GetHandleVerifier [0x0x7ff628520bfd+3035885]
-	GetHandleVerifier [0x0x7ff6285403f0+3164896]
-	GetHandleVerifier [0x0x7ff628268c2e+185118]
-	GetHandleVerifier [0x0x7ff62827053f+216111]
-	GetHandleVerifier [0x0x7ff6282572d4+113092]
-	GetHandleVerifier [0x0x7ff628257489+113529]
-	GetHandleVerifier [0x0x7ff62823e288+10616]
+	GetHandleVerifier [0x0x7ff75762e925+77845]
+	GetHandleVerifier [0x0x7ff75762e980+77936]
+	(No symbol) [0x0x7ff7573e9cda]
+	(No symbol) [0x0x7ff7574406aa]
+	(No symbol) [0x0x7ff75744095c]
+	(No symbol) [0x0x7ff757493d07]
+	(No symbol) [0x0x7ff75746890f]
+	(No symbol) [0x0x7ff757490b07]
+	(No symbol) [0x0x7ff7574686a3]
+	(No symbol) [0x0x7ff757431791]
+	(No symbol) [0x0x7ff757432523]
+	GetHandleVerifier [0x0x7ff75790683d+3059501]
+	GetHandleVerifier [0x0x7ff757900bfd+3035885]
+	GetHandleVerifier [0x0x7ff7579203f0+3164896]
+	GetHandleVerifier [0x0x7ff757648c2e+185118]
+	GetHandleVerifier [0x0x7ff75765053f+216111]
+	GetHandleVerifier [0x0x7ff7576372d4+113092]
+	GetHandleVerifier [0x0x7ff757637489+113529]
+	GetHandleVerifier [0x0x7ff75761e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -2624,25 +2624,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff62824e925+77845]
-	GetHandleVerifier [0x0x7ff62824e980+77936]
-	(No symbol) [0x0x7ff628009cda]
-	(No symbol) [0x0x7ff6280606aa]
-	(No symbol) [0x0x7ff62806095c]
-	(No symbol) [0x0x7ff6280b3d07]
-	(No symbol) [0x0x7ff62808890f]
-	(No symbol) [0x0x7ff6280b0b07]
-	(No symbol) [0x0x7ff6280886a3]
-	(No symbol) [0x0x7ff628051791]
-	(No symbol) [0x0x7ff628052523]
-	GetHandleVerifier [0x0x7ff62852683d+3059501]
-	GetHandleVerifier [0x0x7ff628520bfd+3035885]
-	GetHandleVerifier [0x0x7ff6285403f0+3164896]
-	GetHandleVerifier [0x0x7ff628268c2e+185118]
-	GetHandleVerifier [0x0x7ff62827053f+216111]
-	GetHandleVerifier [0x0x7ff6282572d4+113092]
-	GetHandleVerifier [0x0x7ff628257489+113529]
-	GetHandleVerifier [0x0x7ff62823e288+10616]
+	GetHandleVerifier [0x0x7ff75762e925+77845]
+	GetHandleVerifier [0x0x7ff75762e980+77936]
+	(No symbol) [0x0x7ff7573e9cda]
+	(No symbol) [0x0x7ff7574406aa]
+	(No symbol) [0x0x7ff75744095c]
+	(No symbol) [0x0x7ff757493d07]
+	(No symbol) [0x0x7ff75746890f]
+	(No symbol) [0x0x7ff757490b07]
+	(No symbol) [0x0x7ff7574686a3]
+	(No symbol) [0x0x7ff757431791]
+	(No symbol) [0x0x7ff757432523]
+	GetHandleVerifier [0x0x7ff75790683d+3059501]
+	GetHandleVerifier [0x0x7ff757900bfd+3035885]
+	GetHandleVerifier [0x0x7ff7579203f0+3164896]
+	GetHandleVerifier [0x0x7ff757648c2e+185118]
+	GetHandleVerifier [0x0x7ff75765053f+216111]
+	GetHandleVerifier [0x0x7ff7576372d4+113092]
+	GetHandleVerifier [0x0x7ff757637489+113529]
+	GetHandleVerifier [0x0x7ff75761e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -2745,25 +2745,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff62824e925+77845]
-	GetHandleVerifier [0x0x7ff62824e980+77936]
-	(No symbol) [0x0x7ff628009cda]
-	(No symbol) [0x0x7ff6280606aa]
-	(No symbol) [0x0x7ff62806095c]
-	(No symbol) [0x0x7ff6280b3d07]
-	(No symbol) [0x0x7ff62808890f]
-	(No symbol) [0x0x7ff6280b0b07]
-	(No symbol) [0x0x7ff6280886a3]
-	(No symbol) [0x0x7ff628051791]
-	(No symbol) [0x0x7ff628052523]
-	GetHandleVerifier [0x0x7ff62852683d+3059501]
-	GetHandleVerifier [0x0x7ff628520bfd+3035885]
-	GetHandleVerifier [0x0x7ff6285403f0+3164896]
-	GetHandleVerifier [0x0x7ff628268c2e+185118]
-	GetHandleVerifier [0x0x7ff62827053f+216111]
-	GetHandleVerifier [0x0x7ff6282572d4+113092]
-	GetHandleVerifier [0x0x7ff628257489+113529]
-	GetHandleVerifier [0x0x7ff62823e288+10616]
+	GetHandleVerifier [0x0x7ff75762e925+77845]
+	GetHandleVerifier [0x0x7ff75762e980+77936]
+	(No symbol) [0x0x7ff7573e9cda]
+	(No symbol) [0x0x7ff7574406aa]
+	(No symbol) [0x0x7ff75744095c]
+	(No symbol) [0x0x7ff757493d07]
+	(No symbol) [0x0x7ff75746890f]
+	(No symbol) [0x0x7ff757490b07]
+	(No symbol) [0x0x7ff7574686a3]
+	(No symbol) [0x0x7ff757431791]
+	(No symbol) [0x0x7ff757432523]
+	GetHandleVerifier [0x0x7ff75790683d+3059501]
+	GetHandleVerifier [0x0x7ff757900bfd+3035885]
+	GetHandleVerifier [0x0x7ff7579203f0+3164896]
+	GetHandleVerifier [0x0x7ff757648c2e+185118]
+	GetHandleVerifier [0x0x7ff75765053f+216111]
+	GetHandleVerifier [0x0x7ff7576372d4+113092]
+	GetHandleVerifier [0x0x7ff757637489+113529]
+	GetHandleVerifier [0x0x7ff75761e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -2866,25 +2866,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff62824e925+77845]
-	GetHandleVerifier [0x0x7ff62824e980+77936]
-	(No symbol) [0x0x7ff628009cda]
-	(No symbol) [0x0x7ff6280606aa]
-	(No symbol) [0x0x7ff62806095c]
-	(No symbol) [0x0x7ff6280b3d07]
-	(No symbol) [0x0x7ff62808890f]
-	(No symbol) [0x0x7ff6280b0b07]
-	(No symbol) [0x0x7ff6280886a3]
-	(No symbol) [0x0x7ff628051791]
-	(No symbol) [0x0x7ff628052523]
-	GetHandleVerifier [0x0x7ff62852683d+3059501]
-	GetHandleVerifier [0x0x7ff628520bfd+3035885]
-	GetHandleVerifier [0x0x7ff6285403f0+3164896]
-	GetHandleVerifier [0x0x7ff628268c2e+185118]
-	GetHandleVerifier [0x0x7ff62827053f+216111]
-	GetHandleVerifier [0x0x7ff6282572d4+113092]
-	GetHandleVerifier [0x0x7ff628257489+113529]
-	GetHandleVerifier [0x0x7ff62823e288+10616]
+	GetHandleVerifier [0x0x7ff75762e925+77845]
+	GetHandleVerifier [0x0x7ff75762e980+77936]
+	(No symbol) [0x0x7ff7573e9cda]
+	(No symbol) [0x0x7ff7574406aa]
+	(No symbol) [0x0x7ff75744095c]
+	(No symbol) [0x0x7ff757493d07]
+	(No symbol) [0x0x7ff75746890f]
+	(No symbol) [0x0x7ff757490b07]
+	(No symbol) [0x0x7ff7574686a3]
+	(No symbol) [0x0x7ff757431791]
+	(No symbol) [0x0x7ff757432523]
+	GetHandleVerifier [0x0x7ff75790683d+3059501]
+	GetHandleVerifier [0x0x7ff757900bfd+3035885]
+	GetHandleVerifier [0x0x7ff7579203f0+3164896]
+	GetHandleVerifier [0x0x7ff757648c2e+185118]
+	GetHandleVerifier [0x0x7ff75765053f+216111]
+	GetHandleVerifier [0x0x7ff7576372d4+113092]
+	GetHandleVerifier [0x0x7ff757637489+113529]
+	GetHandleVerifier [0x0x7ff75761e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -2987,25 +2987,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff62824e925+77845]
-	GetHandleVerifier [0x0x7ff62824e980+77936]
-	(No symbol) [0x0x7ff628009cda]
-	(No symbol) [0x0x7ff6280606aa]
-	(No symbol) [0x0x7ff62806095c]
-	(No symbol) [0x0x7ff6280b3d07]
-	(No symbol) [0x0x7ff62808890f]
-	(No symbol) [0x0x7ff6280b0b07]
-	(No symbol) [0x0x7ff6280886a3]
-	(No symbol) [0x0x7ff628051791]
-	(No symbol) [0x0x7ff628052523]
-	GetHandleVerifier [0x0x7ff62852683d+3059501]
-	GetHandleVerifier [0x0x7ff628520bfd+3035885]
-	GetHandleVerifier [0x0x7ff6285403f0+3164896]
-	GetHandleVerifier [0x0x7ff628268c2e+185118]
-	GetHandleVerifier [0x0x7ff62827053f+216111]
-	GetHandleVerifier [0x0x7ff6282572d4+113092]
-	GetHandleVerifier [0x0x7ff628257489+113529]
-	GetHandleVerifier [0x0x7ff62823e288+10616]
+	GetHandleVerifier [0x0x7ff75762e925+77845]
+	GetHandleVerifier [0x0x7ff75762e980+77936]
+	(No symbol) [0x0x7ff7573e9cda]
+	(No symbol) [0x0x7ff7574406aa]
+	(No symbol) [0x0x7ff75744095c]
+	(No symbol) [0x0x7ff757493d07]
+	(No symbol) [0x0x7ff75746890f]
+	(No symbol) [0x0x7ff757490b07]
+	(No symbol) [0x0x7ff7574686a3]
+	(No symbol) [0x0x7ff757431791]
+	(No symbol) [0x0x7ff757432523]
+	GetHandleVerifier [0x0x7ff75790683d+3059501]
+	GetHandleVerifier [0x0x7ff757900bfd+3035885]
+	GetHandleVerifier [0x0x7ff7579203f0+3164896]
+	GetHandleVerifier [0x0x7ff757648c2e+185118]
+	GetHandleVerifier [0x0x7ff75765053f+216111]
+	GetHandleVerifier [0x0x7ff7576372d4+113092]
+	GetHandleVerifier [0x0x7ff757637489+113529]
+	GetHandleVerifier [0x0x7ff75761e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -3108,25 +3108,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff62824e925+77845]
-	GetHandleVerifier [0x0x7ff62824e980+77936]
-	(No symbol) [0x0x7ff628009cda]
-	(No symbol) [0x0x7ff6280606aa]
-	(No symbol) [0x0x7ff62806095c]
-	(No symbol) [0x0x7ff6280b3d07]
-	(No symbol) [0x0x7ff62808890f]
-	(No symbol) [0x0x7ff6280b0b07]
-	(No symbol) [0x0x7ff6280886a3]
-	(No symbol) [0x0x7ff628051791]
-	(No symbol) [0x0x7ff628052523]
-	GetHandleVerifier [0x0x7ff62852683d+3059501]
-	GetHandleVerifier [0x0x7ff628520bfd+3035885]
-	GetHandleVerifier [0x0x7ff6285403f0+3164896]
-	GetHandleVerifier [0x0x7ff628268c2e+185118]
-	GetHandleVerifier [0x0x7ff62827053f+216111]
-	GetHandleVerifier [0x0x7ff6282572d4+113092]
-	GetHandleVerifier [0x0x7ff628257489+113529]
-	GetHandleVerifier [0x0x7ff62823e288+10616]
+	GetHandleVerifier [0x0x7ff75762e925+77845]
+	GetHandleVerifier [0x0x7ff75762e980+77936]
+	(No symbol) [0x0x7ff7573e9cda]
+	(No symbol) [0x0x7ff7574406aa]
+	(No symbol) [0x0x7ff75744095c]
+	(No symbol) [0x0x7ff757493d07]
+	(No symbol) [0x0x7ff75746890f]
+	(No symbol) [0x0x7ff757490b07]
+	(No symbol) [0x0x7ff7574686a3]
+	(No symbol) [0x0x7ff757431791]
+	(No symbol) [0x0x7ff757432523]
+	GetHandleVerifier [0x0x7ff75790683d+3059501]
+	GetHandleVerifier [0x0x7ff757900bfd+3035885]
+	GetHandleVerifier [0x0x7ff7579203f0+3164896]
+	GetHandleVerifier [0x0x7ff757648c2e+185118]
+	GetHandleVerifier [0x0x7ff75765053f+216111]
+	GetHandleVerifier [0x0x7ff7576372d4+113092]
+	GetHandleVerifier [0x0x7ff757637489+113529]
+	GetHandleVerifier [0x0x7ff75761e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -3229,25 +3229,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff62824e925+77845]
-	GetHandleVerifier [0x0x7ff62824e980+77936]
-	(No symbol) [0x0x7ff628009cda]
-	(No symbol) [0x0x7ff6280606aa]
-	(No symbol) [0x0x7ff62806095c]
-	(No symbol) [0x0x7ff6280b3d07]
-	(No symbol) [0x0x7ff62808890f]
-	(No symbol) [0x0x7ff6280b0b07]
-	(No symbol) [0x0x7ff6280886a3]
-	(No symbol) [0x0x7ff628051791]
-	(No symbol) [0x0x7ff628052523]
-	GetHandleVerifier [0x0x7ff62852683d+3059501]
-	GetHandleVerifier [0x0x7ff628520bfd+3035885]
-	GetHandleVerifier [0x0x7ff6285403f0+3164896]
-	GetHandleVerifier [0x0x7ff628268c2e+185118]
-	GetHandleVerifier [0x0x7ff62827053f+216111]
-	GetHandleVerifier [0x0x7ff6282572d4+113092]
-	GetHandleVerifier [0x0x7ff628257489+113529]
-	GetHandleVerifier [0x0x7ff62823e288+10616]
+	GetHandleVerifier [0x0x7ff75762e925+77845]
+	GetHandleVerifier [0x0x7ff75762e980+77936]
+	(No symbol) [0x0x7ff7573e9cda]
+	(No symbol) [0x0x7ff7574406aa]
+	(No symbol) [0x0x7ff75744095c]
+	(No symbol) [0x0x7ff757493d07]
+	(No symbol) [0x0x7ff75746890f]
+	(No symbol) [0x0x7ff757490b07]
+	(No symbol) [0x0x7ff7574686a3]
+	(No symbol) [0x0x7ff757431791]
+	(No symbol) [0x0x7ff757432523]
+	GetHandleVerifier [0x0x7ff75790683d+3059501]
+	GetHandleVerifier [0x0x7ff757900bfd+3035885]
+	GetHandleVerifier [0x0x7ff7579203f0+3164896]
+	GetHandleVerifier [0x0x7ff757648c2e+185118]
+	GetHandleVerifier [0x0x7ff75765053f+216111]
+	GetHandleVerifier [0x0x7ff7576372d4+113092]
+	GetHandleVerifier [0x0x7ff757637489+113529]
+	GetHandleVerifier [0x0x7ff75761e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -3350,25 +3350,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff62824e925+77845]
-	GetHandleVerifier [0x0x7ff62824e980+77936]
-	(No symbol) [0x0x7ff628009cda]
-	(No symbol) [0x0x7ff6280606aa]
-	(No symbol) [0x0x7ff62806095c]
-	(No symbol) [0x0x7ff6280b3d07]
-	(No symbol) [0x0x7ff62808890f]
-	(No symbol) [0x0x7ff6280b0b07]
-	(No symbol) [0x0x7ff6280886a3]
-	(No symbol) [0x0x7ff628051791]
-	(No symbol) [0x0x7ff628052523]
-	GetHandleVerifier [0x0x7ff62852683d+3059501]
-	GetHandleVerifier [0x0x7ff628520bfd+3035885]
-	GetHandleVerifier [0x0x7ff6285403f0+3164896]
-	GetHandleVerifier [0x0x7ff628268c2e+185118]
-	GetHandleVerifier [0x0x7ff62827053f+216111]
-	GetHandleVerifier [0x0x7ff6282572d4+113092]
-	GetHandleVerifier [0x0x7ff628257489+113529]
-	GetHandleVerifier [0x0x7ff62823e288+10616]
+	GetHandleVerifier [0x0x7ff75762e925+77845]
+	GetHandleVerifier [0x0x7ff75762e980+77936]
+	(No symbol) [0x0x7ff7573e9cda]
+	(No symbol) [0x0x7ff7574406aa]
+	(No symbol) [0x0x7ff75744095c]
+	(No symbol) [0x0x7ff757493d07]
+	(No symbol) [0x0x7ff75746890f]
+	(No symbol) [0x0x7ff757490b07]
+	(No symbol) [0x0x7ff7574686a3]
+	(No symbol) [0x0x7ff757431791]
+	(No symbol) [0x0x7ff757432523]
+	GetHandleVerifier [0x0x7ff75790683d+3059501]
+	GetHandleVerifier [0x0x7ff757900bfd+3035885]
+	GetHandleVerifier [0x0x7ff7579203f0+3164896]
+	GetHandleVerifier [0x0x7ff757648c2e+185118]
+	GetHandleVerifier [0x0x7ff75765053f+216111]
+	GetHandleVerifier [0x0x7ff7576372d4+113092]
+	GetHandleVerifier [0x0x7ff757637489+113529]
+	GetHandleVerifier [0x0x7ff75761e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -3471,25 +3471,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff62824e925+77845]
-	GetHandleVerifier [0x0x7ff62824e980+77936]
-	(No symbol) [0x0x7ff628009cda]
-	(No symbol) [0x0x7ff6280606aa]
-	(No symbol) [0x0x7ff62806095c]
-	(No symbol) [0x0x7ff6280b3d07]
-	(No symbol) [0x0x7ff62808890f]
-	(No symbol) [0x0x7ff6280b0b07]
-	(No symbol) [0x0x7ff6280886a3]
-	(No symbol) [0x0x7ff628051791]
-	(No symbol) [0x0x7ff628052523]
-	GetHandleVerifier [0x0x7ff62852683d+3059501]
-	GetHandleVerifier [0x0x7ff628520bfd+3035885]
-	GetHandleVerifier [0x0x7ff6285403f0+3164896]
-	GetHandleVerifier [0x0x7ff628268c2e+185118]
-	GetHandleVerifier [0x0x7ff62827053f+216111]
-	GetHandleVerifier [0x0x7ff6282572d4+113092]
-	GetHandleVerifier [0x0x7ff628257489+113529]
-	GetHandleVerifier [0x0x7ff62823e288+10616]
+	GetHandleVerifier [0x0x7ff75762e925+77845]
+	GetHandleVerifier [0x0x7ff75762e980+77936]
+	(No symbol) [0x0x7ff7573e9cda]
+	(No symbol) [0x0x7ff7574406aa]
+	(No symbol) [0x0x7ff75744095c]
+	(No symbol) [0x0x7ff757493d07]
+	(No symbol) [0x0x7ff75746890f]
+	(No symbol) [0x0x7ff757490b07]
+	(No symbol) [0x0x7ff7574686a3]
+	(No symbol) [0x0x7ff757431791]
+	(No symbol) [0x0x7ff757432523]
+	GetHandleVerifier [0x0x7ff75790683d+3059501]
+	GetHandleVerifier [0x0x7ff757900bfd+3035885]
+	GetHandleVerifier [0x0x7ff7579203f0+3164896]
+	GetHandleVerifier [0x0x7ff757648c2e+185118]
+	GetHandleVerifier [0x0x7ff75765053f+216111]
+	GetHandleVerifier [0x0x7ff7576372d4+113092]
+	GetHandleVerifier [0x0x7ff757637489+113529]
+	GetHandleVerifier [0x0x7ff75761e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -3559,7 +3559,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>£1184.0</t>
+          <t>£1160.0</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3656,7 +3656,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>POA or Product 'out of stock'</t>
+          <t>£1296.0</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3753,7 +3753,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>POA or Product 'out of stock'</t>
+          <t>£1280.0</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
